--- a/budget/Suivi_budgetaire_Monique_Festival.xlsx
+++ b/budget/Suivi_budgetaire_Monique_Festival.xlsx
@@ -825,11 +825,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>'F&amp;B'!D13</f>
+        <f>'F&amp;B'!D16</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>'F&amp;B'!E13</f>
+        <f>'F&amp;B'!E16</f>
         <v/>
       </c>
       <c r="D6" s="3">
@@ -837,11 +837,11 @@
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>'F&amp;B'!D27</f>
+        <f>'F&amp;B'!D57</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>'F&amp;B'!E27</f>
+        <f>'F&amp;B'!E57</f>
         <v/>
       </c>
       <c r="G6" s="4">

--- a/budget/Suivi_budgetaire_Monique_Festival.xlsx
+++ b/budget/Suivi_budgetaire_Monique_Festival.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ \€"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +100,15 @@
     </font>
     <font>
       <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001F4E78"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -240,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -299,6 +308,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -664,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="35" customWidth="1" style="18" min="1" max="1"/>
@@ -1095,13 +1106,13 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>47464</v>
+        <v>46403</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>47767</v>
+        <v>49667</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>-303</v>
+        <v>-3264</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -1119,13 +1130,13 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>58482</v>
+        <v>57421</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>49907</v>
+        <v>51807</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>8575</v>
+        <v>5614</v>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
@@ -1143,13 +1154,13 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>69500</v>
+        <v>68439</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>52048</v>
+        <v>53948</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>17453</v>
+        <v>14491</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
@@ -1158,6 +1169,37 @@
       </c>
       <c r="F20" s="8" t="n">
         <v>1440</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>Standard + réassort bière 5 fûts</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="n">
+        <v>60621</v>
+      </c>
+      <c r="C22" s="38" t="n">
+        <v>52207</v>
+      </c>
+      <c r="D22" s="38" t="n">
+        <v>8414</v>
+      </c>
+      <c r="E22" s="38" t="inlineStr">
+        <is>
+          <t>1 200</t>
+        </is>
+      </c>
+      <c r="F22" s="38" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>Note : SACEM 1 427 € et repas artistes 555 € exclus du F&amp;B (à imputer Droits d auteur / Artistes si confirmes dus)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/budget/Suivi_budgetaire_Monique_Festival.xlsx
+++ b/budget/Suivi_budgetaire_Monique_Festival.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ \€"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -110,6 +110,16 @@
       <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="16">
@@ -249,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -310,6 +320,15 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5189,179 +5208,2022 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:F104"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" style="18" min="1" max="1"/>
-    <col width="13" customWidth="1" style="18" min="2" max="2"/>
-    <col width="15" customWidth="1" style="18" min="3" max="3"/>
-    <col width="16" customWidth="1" style="18" min="4" max="6"/>
+    <col width="14" customWidth="1" style="18" min="1" max="1"/>
+    <col width="16" customWidth="1" style="18" min="2" max="2"/>
+    <col width="70" customWidth="1" style="18" min="3" max="3"/>
+    <col width="13" customWidth="1" style="18" min="4" max="4"/>
+    <col width="13" customWidth="1" style="18" min="5" max="5"/>
+    <col width="14" customWidth="1" style="18" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" customHeight="1" s="18">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>TRÉSORERIE — Flux par date</t>
+    <row r="1" ht="24" customHeight="1" s="18">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>TRÉSORERIE — Plan détaillé des dépenses pré-festival (mai → août 2026)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Solde initial</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>FLUX HISTORIQUES (déjà passés au 03/05/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Entrée</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Sortie</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>Solde</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>Crowdfunding HelloAsso</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>Cumul dons collectés au 23/04 (14 dons)</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="n">
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Crowdfunding</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Cumul 14 dons HelloAsso au 23/04</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="n">
         <v>845</v>
       </c>
-      <c r="E4" s="22" t="inlineStr"/>
-      <c r="F4" s="22">
-        <f>D2+D4-E4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Don manuel Charles</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Don Charles</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Don manuel par virement Qonto</t>
         </is>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D7" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" s="22" t="inlineStr"/>
-      <c r="F5" s="22">
-        <f>F4+D5-E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Avr-Mai 2026</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Frais divers</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>Petites dépenses opérationnelles (cumul estimation)</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="n">
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>Petites dépenses opérationnelles cumul (cartes de visite, frais admin)</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n">
         <v>255</v>
       </c>
-      <c r="F6" s="22">
-        <f>F5+D6-E6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="F8" s="29" t="n">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Crowdfunding HelloAsso</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Crowdfunding</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Cumul dons supplémentaires (23/04 → 01/05)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D9" s="29" t="n">
         <v>360</v>
       </c>
-      <c r="E7" s="22" t="inlineStr"/>
-      <c r="F7" s="22">
-        <f>F6+D7-E7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>TOTAUX</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23">
-        <f>SUM(D4:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="23">
-        <f>SUM(E4:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="23">
-        <f>F7</f>
-        <v/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n">
+        <v>1950</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>SOLDE Qonto au 01/05/2026 (estimation)</t>
-        </is>
-      </c>
-      <c r="F10" s="25">
-        <f>F7</f>
-        <v/>
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>SOLDE Qonto estimé au 03/05/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="30" t="n"/>
+      <c r="F10" s="30" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>MAI 2026 — Dépenses prévues</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Échéance</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Pôle</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Montant prévu</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Souscription assurance RC pro festival (prime annuelle estimative)</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>800</v>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F15" s="29" t="inlineStr">
+        <is>
+          <t>Cible AIAC ou MAIF — 600-1000 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n"/>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Cartes de visite Pixartprinting (commande passée 30/04)</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F16" s="29" t="inlineStr">
+        <is>
+          <t>Pour collecte mécénat</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Frais postaux LRAR rescrit DDFIP + courriers partenaires</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>Recommandé +AR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total MAI 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="30">
+        <f>SUM(D15:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="30" t="n"/>
+      <c r="F18" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>JUIN 2026 — Dépenses prévues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Échéance</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>Pôle</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D22" s="28" t="inlineStr">
+        <is>
+          <t>Montant prévu</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>1ère vague affiches + flyers (impression Pixartprinting)</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>500</v>
+      </c>
+      <c r="E23" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F23" s="29" t="inlineStr">
+        <is>
+          <t>Lancement com programmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n"/>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% Location salle La Grange Huguenet</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>900</v>
+      </c>
+      <c r="E24" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F24" s="29" t="inlineStr">
+        <is>
+          <t>Sur 3000 € total</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n"/>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% Sonorisation</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>900</v>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>Sur 3000 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% Éclairage / lumière</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>600</v>
+      </c>
+      <c r="E26" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F26" s="29" t="inlineStr">
+        <is>
+          <t>Sur 2000 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% Scène / podium</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="n">
+        <v>600</v>
+      </c>
+      <c r="E27" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F27" s="29" t="inlineStr">
+        <is>
+          <t>Sur 2000 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="n"/>
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>Commande écocups Atomic 1000 unités</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>600</v>
+      </c>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F28" s="29" t="inlineStr">
+        <is>
+          <t>Délai livraison ~3 semaines</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="n"/>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>Commande jetons flousy ~5000 unités</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="n">
+        <v>400</v>
+      </c>
+      <c r="E29" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F29" s="29" t="inlineStr">
+        <is>
+          <t>Stock {1×2000, 2×1000, 5×1500, 10×500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% Machine pop-corn (location)</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="n">
+        <v>80</v>
+      </c>
+      <c r="E30" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F30" s="29" t="inlineStr">
+        <is>
+          <t>Sur 252 € total</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% cachets artistes locaux/régionaux (signature contrats)</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E31" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F31" s="29" t="inlineStr">
+        <is>
+          <t>Sur ~7000 € locaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="n"/>
+      <c r="B32" s="30" t="n"/>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total JUIN 2026</t>
+        </is>
+      </c>
+      <c r="D32" s="30">
+        <f>SUM(D23:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="30" t="n"/>
+      <c r="F32" s="30" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>JUILLET 2026 — Dépenses prévues</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>Échéance</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>Pôle</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>Montant prévu</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="F36" s="28" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="n"/>
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>2ème vague communication + vidéo promo</t>
+        </is>
+      </c>
+      <c r="D37" s="29" t="n">
+        <v>500</v>
+      </c>
+      <c r="E37" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F37" s="29" t="inlineStr">
+        <is>
+          <t>Final push avant festival</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="n"/>
+      <c r="B38" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% Toilettes / sanitaires</t>
+        </is>
+      </c>
+      <c r="D38" s="29" t="n">
+        <v>450</v>
+      </c>
+      <c r="E38" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F38" s="29" t="inlineStr">
+        <is>
+          <t>Sur 1500 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="n"/>
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% Électricité / groupe électrogène</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="n">
+        <v>450</v>
+      </c>
+      <c r="E39" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F39" s="29" t="inlineStr">
+        <is>
+          <t>Sur 1500 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="n"/>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% Barrières / sécurité</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>300</v>
+      </c>
+      <c r="E40" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F40" s="29" t="inlineStr">
+        <is>
+          <t>Sur 1000 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="n"/>
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 30% Mobilier (tables, chaises, tentes)</t>
+        </is>
+      </c>
+      <c r="D41" s="29" t="n">
+        <v>300</v>
+      </c>
+      <c r="E41" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F41" s="29" t="inlineStr">
+        <is>
+          <t>Sur 1000 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="n"/>
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>Répétitions Fabulo (4 art × 2 jours × 100 €)</t>
+        </is>
+      </c>
+      <c r="D42" s="29" t="n">
+        <v>800</v>
+      </c>
+      <c r="E42" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F42" s="29" t="inlineStr">
+        <is>
+          <t>Préparation collectif Fabulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="n"/>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>Répétitions Atelier écriture — Sylvain (2j × 100 €)</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="E43" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F43" s="29" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="n"/>
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>Répétitions Atelier DJ — Jeff (2j × 100 €)</t>
+        </is>
+      </c>
+      <c r="D44" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="E44" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F44" s="29" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="n"/>
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>Avance défraiement artistes étrangers (50% billets early)</t>
+        </is>
+      </c>
+      <c r="D45" s="29" t="n">
+        <v>600</v>
+      </c>
+      <c r="E45" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F45" s="29" t="inlineStr">
+        <is>
+          <t>Pour booking train/avion avant 15/06 deadline</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="n"/>
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>Acompte 20% supplémentaire cachets nationaux</t>
+        </is>
+      </c>
+      <c r="D46" s="29" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E46" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F46" s="29" t="inlineStr">
+        <is>
+          <t>Confirmation contrats</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="n"/>
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>Vaisselle bio jetable (gobelets, assiettes, serviettes)</t>
+        </is>
+      </c>
+      <c r="D47" s="29" t="n">
+        <v>319</v>
+      </c>
+      <c r="E47" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F47" s="29" t="inlineStr">
+        <is>
+          <t>Stock pour J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="n"/>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>HACCP (tablier, gants, sondes T°) + caisse + ustensiles préparation</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="n">
+        <v>540</v>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="inlineStr">
+        <is>
+          <t>Préparation stand</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="30" t="n"/>
+      <c r="B49" s="30" t="n"/>
+      <c r="C49" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total JUILLET 2026</t>
+        </is>
+      </c>
+      <c r="D49" s="30">
+        <f>SUM(D37:D48)</f>
+        <v/>
+      </c>
+      <c r="E49" s="30" t="n"/>
+      <c r="F49" s="30" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>AOÛT 2026 (avant festival 28/08) — Dépenses prévues</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>Échéance</t>
+        </is>
+      </c>
+      <c r="B53" s="28" t="inlineStr">
+        <is>
+          <t>Pôle</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D53" s="28" t="inlineStr">
+        <is>
+          <t>Montant prévu</t>
+        </is>
+      </c>
+      <c r="E53" s="28" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="F53" s="28" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="29" t="n"/>
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Location salle La Grange Huguenet</t>
+        </is>
+      </c>
+      <c r="D54" s="29" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E54" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F54" s="29" t="inlineStr">
+        <is>
+          <t>Au montage</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="29" t="n"/>
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C55" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Sonorisation</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E55" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F55" s="29" t="inlineStr">
+        <is>
+          <t>Au montage J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="29" t="n"/>
+      <c r="B56" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C56" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Éclairage / lumière</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E56" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F56" s="29" t="inlineStr">
+        <is>
+          <t>Au montage J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="n"/>
+      <c r="B57" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C57" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Scène / podium</t>
+        </is>
+      </c>
+      <c r="D57" s="29" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F57" s="29" t="inlineStr">
+        <is>
+          <t>Au montage J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="n"/>
+      <c r="B58" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C58" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Toilettes / sanitaires</t>
+        </is>
+      </c>
+      <c r="D58" s="29" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E58" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F58" s="29" t="inlineStr">
+        <is>
+          <t>Au montage J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="n"/>
+      <c r="B59" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Électricité / groupe électrogène</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E59" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F59" s="29" t="inlineStr">
+        <is>
+          <t>Au montage J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="n"/>
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Barrières / sécurité</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="n">
+        <v>700</v>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F60" s="29" t="inlineStr">
+        <is>
+          <t>Au montage J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="n"/>
+      <c r="B61" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Mobilier (tables, chaises, tentes)</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="n">
+        <v>700</v>
+      </c>
+      <c r="E61" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F61" s="29" t="inlineStr">
+        <is>
+          <t>Au montage J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="n"/>
+      <c r="B62" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>Solde Machine pop-corn (location)</t>
+        </is>
+      </c>
+      <c r="D62" s="29" t="n">
+        <v>172</v>
+      </c>
+      <c r="E62" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F62" s="29" t="inlineStr">
+        <is>
+          <t>Au montage</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="n"/>
+      <c r="B63" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>Percolateurs 4×10L ABC LOCATION</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="n">
+        <v>345</v>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F63" s="29" t="inlineStr">
+        <is>
+          <t>Réservation + livraison J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="29" t="n"/>
+      <c r="B64" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>Friteuses ×2 ABC LOCATION</t>
+        </is>
+      </c>
+      <c r="D64" s="29" t="n">
+        <v>172</v>
+      </c>
+      <c r="E64" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F64" s="29" t="inlineStr">
+        <is>
+          <t>Réservation + livraison J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="n"/>
+      <c r="B65" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C65" s="29" t="inlineStr">
+        <is>
+          <t>Eau gratuite — fontaines + carafes</t>
+        </is>
+      </c>
+      <c r="D65" s="29" t="n">
+        <v>400</v>
+      </c>
+      <c r="E65" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F65" s="29" t="inlineStr">
+        <is>
+          <t>Location J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="n"/>
+      <c r="B66" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>Trousse premiers secours buvette + affichage</t>
+        </is>
+      </c>
+      <c r="D66" s="29" t="n">
+        <v>60</v>
+      </c>
+      <c r="E66" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F66" s="29" t="inlineStr">
+        <is>
+          <t>Préparation stand</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="n"/>
+      <c r="B67" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C67" s="29" t="inlineStr">
+        <is>
+          <t>Sacs poubelles tri + lavage écocups + récup huile</t>
+        </is>
+      </c>
+      <c r="D67" s="29" t="n">
+        <v>120</v>
+      </c>
+      <c r="E67" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F67" s="29" t="inlineStr">
+        <is>
+          <t>Stand + préparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="n"/>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>Bière Le Pintadier — 10 fûts initial</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="n">
+        <v>800</v>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-3, livraison J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="n"/>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>Vin Cubi Jura — 29 cubis (Hyper Boisson)</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="29" t="n"/>
+      <c r="B70" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>Soft (sirop + jus + Mortuacienne + eaux 1L verre)</t>
+        </is>
+      </c>
+      <c r="D70" s="29" t="n">
+        <v>775</v>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F70" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="n"/>
+      <c r="B71" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>Café moulu équitable BFC + sucre + lait + mélangeurs + gobelets</t>
+        </is>
+      </c>
+      <c r="D71" s="29" t="n">
+        <v>110</v>
+      </c>
+      <c r="E71" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F71" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="29" t="n"/>
+      <c r="B72" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>Sucre bar additionnel + glace pilée</t>
+        </is>
+      </c>
+      <c r="D72" s="29" t="n">
+        <v>60</v>
+      </c>
+      <c r="E72" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F72" s="29" t="inlineStr">
+        <is>
+          <t>Achat J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="n"/>
+      <c r="B73" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>Assiettes : fromage Hôpitaux Vieux + Comté/Morbier (~70 kg)</t>
+        </is>
+      </c>
+      <c r="D73" s="29" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E73" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F73" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-3, livraison J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="n"/>
+      <c r="B74" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>Assiettes : charcuterie Ferme Ligny (~77 kg)</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E74" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F74" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-3, livraison J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="n"/>
+      <c r="B75" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C75" s="29" t="inlineStr">
+        <is>
+          <t>Œufs Saveur de la Ferme (3 plateaux 360 + extras)</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="E75" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F75" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-3, livraison J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="29" t="n"/>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>Pain La Ronde des Pains (~110 pains 350g)</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="n">
+        <v>245</v>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-3, livraison J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="n"/>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>Tomates cerise BRUNO BFC (~75 kg, restauration + snack)</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="n">
+        <v>90</v>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-3, livraison J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="29" t="n"/>
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>Pommes de terre BFC (~50 kg pour frites snack + grandes assiettes)</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="n">
+        <v>60</v>
+      </c>
+      <c r="E78" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F78" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-3, livraison J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="29" t="n"/>
+      <c r="B79" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C79" s="29" t="inlineStr">
+        <is>
+          <t>Sachets sous vide Ferme Ligny + autres consommables resto</t>
+        </is>
+      </c>
+      <c r="D79" s="29" t="n">
+        <v>50</v>
+      </c>
+      <c r="E79" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F79" s="29" t="inlineStr">
+        <is>
+          <t>Avec commande charcuterie</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="29" t="n"/>
+      <c r="B80" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C80" s="29" t="inlineStr">
+        <is>
+          <t>Pop-corn (maïs 10kg + huile + sel + gobelets bio 72cL)</t>
+        </is>
+      </c>
+      <c r="D80" s="29" t="n">
+        <v>63</v>
+      </c>
+      <c r="E80" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F80" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="29" t="n"/>
+      <c r="B81" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C81" s="29" t="inlineStr">
+        <is>
+          <t>Frites snack (huile friture + sel + barquettes kraft + sticks sauces)</t>
+        </is>
+      </c>
+      <c r="D81" s="29" t="n">
+        <v>88</v>
+      </c>
+      <c r="E81" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F81" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-7 (pdt comptées séparément)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="29" t="n"/>
+      <c r="B82" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>Glaces ERHARD (43 bacs 2,5L)</t>
+        </is>
+      </c>
+      <c r="D82" s="29" t="n">
+        <v>101</v>
+      </c>
+      <c r="E82" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F82" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-3, livraison J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="29" t="n"/>
+      <c r="B83" s="29" t="inlineStr">
+        <is>
+          <t>F&amp;B</t>
+        </is>
+      </c>
+      <c r="C83" s="29" t="inlineStr">
+        <is>
+          <t>Cornets gaufrette comestibles (560 unités) + back-up</t>
+        </is>
+      </c>
+      <c r="D83" s="29" t="n">
+        <v>70</v>
+      </c>
+      <c r="E83" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F83" s="29" t="inlineStr">
+        <is>
+          <t>Commande J-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="29" t="n"/>
+      <c r="B84" s="29" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C84" s="29" t="inlineStr">
+        <is>
+          <t>Solde 50% cachets artistes (à régler post-prestation J+7)</t>
+        </is>
+      </c>
+      <c r="D84" s="29" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E84" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F84" s="29" t="inlineStr">
+        <is>
+          <t>Prévoir en trésorerie même si paiement J+7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="29" t="n"/>
+      <c r="B85" s="29" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C85" s="29" t="inlineStr">
+        <is>
+          <t>Défraiement étrangers solde (sur réception justificatifs)</t>
+        </is>
+      </c>
+      <c r="D85" s="29" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E85" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F85" s="29" t="inlineStr">
+        <is>
+          <t>Solde après réception tickets, payable J ou J+7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="n"/>
+      <c r="B86" s="29" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C86" s="29" t="inlineStr">
+        <is>
+          <t>Frais administratifs divers (encres, fournitures bureau)</t>
+        </is>
+      </c>
+      <c r="D86" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E86" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F86" s="29" t="inlineStr">
+        <is>
+          <t>Préparation festival</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="29" t="n"/>
+      <c r="B87" s="29" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C87" s="29" t="inlineStr">
+        <is>
+          <t>Imprévus de dernière minute (provision)</t>
+        </is>
+      </c>
+      <c r="D87" s="29" t="n">
+        <v>500</v>
+      </c>
+      <c r="E87" s="29" t="inlineStr">
+        <is>
+          <t>Prévu</t>
+        </is>
+      </c>
+      <c r="F87" s="29" t="inlineStr">
+        <is>
+          <t>Aléas</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="30" t="n"/>
+      <c r="B88" s="30" t="n"/>
+      <c r="C88" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total AOÛT 2026 (avant festival 28/08)</t>
+        </is>
+      </c>
+      <c r="D88" s="30">
+        <f>SUM(D54:D87)</f>
+        <v/>
+      </c>
+      <c r="E88" s="30" t="n"/>
+      <c r="F88" s="30" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL DÉPENSES PRÉ-FESTIVAL (mai-août avant 28/08)</t>
+        </is>
+      </c>
+      <c r="B90" s="41" t="n"/>
+      <c r="C90" s="41" t="n"/>
+      <c r="D90" s="42" t="n">
+        <v>40650</v>
+      </c>
+      <c r="E90" s="41" t="n"/>
+      <c r="F90" s="41" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="36" t="inlineStr">
+        <is>
+          <t>NOTES &amp; HYPOTHÈSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1" s="18">
+      <c r="A93" s="37" t="inlineStr">
+        <is>
+          <t>• Solde Qonto au 03/05/2026 : 1950 € — Besoin de trésorerie cumulé jusqu'au 27/08 : 40650 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1" s="18">
+      <c r="A94" s="37" t="inlineStr">
+        <is>
+          <t>• Gap à financer : 38700 € via crowdfunding + mécénat + subventions + early bird billetterie</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1" s="18">
+      <c r="A95" s="37" t="inlineStr">
+        <is>
+          <t>• Hypothèses fournisseurs : acompte 30% à la commande / solde 70% au montage (à confirmer avec chaque devis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1" s="18">
+      <c r="A96" s="37" t="inlineStr">
+        <is>
+          <t>• Cachets artistes : 30% acompte signature contrat, 50% post-prestation J+7 (à confirmer convention)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1" s="18">
+      <c r="A97" s="37" t="inlineStr">
+        <is>
+          <t>• Défraiement étrangers : avance possible 50% pour booking précoce, solde sur justificatifs</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1" s="18">
+      <c r="A98" s="37" t="inlineStr">
+        <is>
+          <t>• Matières fraîches F&amp;B : commandées J-3 (hors période 'pré-festival' stricte mais cash sortant avant recettes billetterie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1" s="18">
+      <c r="A99" s="37" t="inlineStr">
+        <is>
+          <t>• SACEM Billetterie 1 993 € : payée septembre 2026 (post-festival, sur recettes réelles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1" s="18">
+      <c r="A100" s="37" t="inlineStr">
+        <is>
+          <t>• SACEM Buvette 1 427 € : exclue (à confirmer non due)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1" s="18">
+      <c r="A101" s="37" t="inlineStr">
+        <is>
+          <t>• Repas artistes 555 € : à imputer budget Artistes (non doublonné ici)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="43" t="inlineStr">
+        <is>
+          <t>POUR INFO — Dépenses POST-festival (non comptées ci-dessus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="44" t="n"/>
+      <c r="B104" s="44" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C104" s="44" t="inlineStr">
+        <is>
+          <t>SACEM Billetterie 8.8% (déclaration post-event)</t>
+        </is>
+      </c>
+      <c r="D104" s="44" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E104" s="44" t="n"/>
+      <c r="F104" s="44" t="inlineStr">
+        <is>
+          <t>Septembre 2026 — sur recettes billetterie réelles</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="17">
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A95:F95"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B5:B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Choisir une catégorie" type="list">
-      <formula1>"Crowdfunding,Billetterie,F&amp;B,Ateliers,Artistes,Logistique,Frais divers"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/budget/Suivi_budgetaire_Monique_Festival.xlsx
+++ b/budget/Suivi_budgetaire_Monique_Festival.xlsx
@@ -122,7 +122,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -203,8 +203,38 @@
         <fgColor rgb="000277BD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCDD2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -255,11 +285,55 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -329,6 +403,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -855,11 +941,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>'F&amp;B'!D16</f>
+        <f>'F&amp;B'!H119</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>'F&amp;B'!E16</f>
+        <f>'F&amp;B'!I119</f>
         <v/>
       </c>
       <c r="D6" s="3">
@@ -867,11 +953,11 @@
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>'F&amp;B'!D57</f>
+        <f>'F&amp;B'!H120</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>'F&amp;B'!E57</f>
+        <f>'F&amp;B'!I120</f>
         <v/>
       </c>
       <c r="G6" s="4">
@@ -1655,1069 +1741,4192 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="18" min="1" max="1"/>
-    <col width="75" customWidth="1" style="18" min="2" max="2"/>
-    <col width="12" customWidth="1" style="18" min="3" max="3"/>
-    <col width="12" customWidth="1" style="18" min="4" max="4"/>
-    <col width="12" customWidth="1" style="18" min="5" max="5"/>
-    <col width="12" customWidth="1" style="18" min="6" max="6"/>
+    <col width="11" customWidth="1" style="18" min="1" max="1"/>
+    <col width="22" customWidth="1" style="18" min="2" max="2"/>
+    <col width="50" customWidth="1" style="18" min="3" max="3"/>
+    <col width="24" customWidth="1" style="18" min="4" max="4"/>
+    <col width="9" customWidth="1" style="18" min="5" max="5"/>
+    <col width="9" customWidth="1" style="18" min="6" max="6"/>
+    <col width="9" customWidth="1" style="18" min="7" max="7"/>
+    <col width="11" customWidth="1" style="18" min="8" max="8"/>
+    <col width="24" customWidth="1" style="18" min="9" max="9"/>
+    <col width="35" customWidth="1" style="18" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" s="18">
       <c r="A1" s="26" t="inlineStr">
         <is>
-          <t>F&amp;B — Buvettes + Restauration (Scénario B — validé 03/05/2026)</t>
+          <t>F&amp;B — Buvettes + Restauration (détail max — Scénario B + Flousy)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>RECETTES par jour</t>
+          <t>RECETTES — Détail par jour et par produit</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Jour</t>
         </is>
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Catégorie</t>
         </is>
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
+          <t>Produit</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>Prix flousy</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>Prix €</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="inlineStr">
+        <is>
+          <t>Recette €</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>Bière blonde/blanche Le Pintadier</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E6" s="45" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="45" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B7" s="45" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>Vin Cubi Jura tradition</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E7" s="45" t="n">
+        <v>108</v>
+      </c>
+      <c r="F7" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" s="45" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="inlineStr">
+        <is>
+          <t>Sirop dilué</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E8" s="45" t="n">
+        <v>146</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="45" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>Jus de pomme Saveur de la Ferme</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E9" s="45" t="n">
+        <v>73</v>
+      </c>
+      <c r="F9" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="45" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>Mortuacienne (limonade)</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E10" s="45" t="n">
+        <v>29</v>
+      </c>
+      <c r="F10" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="45" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>Eau pétillante Bisontine</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="inlineStr">
+        <is>
+          <t>Btl verre 1 L</t>
+        </is>
+      </c>
+      <c r="E11" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="45" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>Eau plate (BFC)</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="inlineStr">
+        <is>
+          <t>Btl verre 1 L</t>
+        </is>
+      </c>
+      <c r="E12" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="45" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>Café moulu équitable BFC</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>40</v>
+      </c>
+      <c r="F13" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="45" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>Pop-corn</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="inlineStr">
+        <is>
+          <t>Gobelet 72 cL</t>
+        </is>
+      </c>
+      <c r="E14" s="45" t="n">
+        <v>40</v>
+      </c>
+      <c r="F14" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H14" s="45" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>Frites (snack à part)</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="inlineStr">
+        <is>
+          <t>Barquette kraft 150 g</t>
+        </is>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="45" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>Glace 1 boule</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="inlineStr">
+        <is>
+          <t>Cornet gaufrette</t>
+        </is>
+      </c>
+      <c r="E16" s="45" t="n">
+        <v>31</v>
+      </c>
+      <c r="F16" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="45" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B17" s="45" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>Glace 2 boules</t>
+        </is>
+      </c>
+      <c r="D17" s="45" t="inlineStr">
+        <is>
+          <t>Cornet gaufrette</t>
+        </is>
+      </c>
+      <c r="E17" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="F17" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="45" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>Tomates cerise BRUNO</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="inlineStr">
+        <is>
+          <t>Gobelet 25 cL (150 g)</t>
+        </is>
+      </c>
+      <c r="E18" s="45" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="45" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>Petite assiette franc-comtoise</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="E19" s="45" t="n">
+        <v>47</v>
+      </c>
+      <c r="F19" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" s="45" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C20" s="45" t="inlineStr">
+        <is>
+          <t>Petite assiette végétarienne</t>
+        </is>
+      </c>
+      <c r="D20" s="45" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="E20" s="45" t="n">
+        <v>21</v>
+      </c>
+      <c r="F20" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" s="45" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C21" s="45" t="inlineStr">
+        <is>
+          <t>Grande assiette franc-comtoise</t>
+        </is>
+      </c>
+      <c r="D21" s="45" t="inlineStr">
+        <is>
+          <t>Plateau + frites</t>
+        </is>
+      </c>
+      <c r="E21" s="45" t="n">
+        <v>110</v>
+      </c>
+      <c r="F21" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" s="45" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="inlineStr">
+        <is>
+          <t>Grande assiette végétarienne</t>
+        </is>
+      </c>
+      <c r="D22" s="45" t="inlineStr">
+        <is>
+          <t>Plateau + frites</t>
+        </is>
+      </c>
+      <c r="E22" s="45" t="n">
+        <v>47</v>
+      </c>
+      <c r="F22" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" s="45" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B23" s="45" t="inlineStr">
+        <is>
+          <t>Consommables</t>
+        </is>
+      </c>
+      <c r="C23" s="45" t="inlineStr">
+        <is>
+          <t>Consigne écocup non remboursée</t>
+        </is>
+      </c>
+      <c r="D23" s="45" t="inlineStr">
+        <is>
+          <t>Jeton</t>
+        </is>
+      </c>
+      <c r="E23" s="45" t="n">
+        <v>41</v>
+      </c>
+      <c r="F23" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H23" s="45" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total Vendredi</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+      <c r="H24" s="30">
+        <f>SUM(H6:H23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>Bière blonde/blanche Le Pintadier</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E25" s="46" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F25" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H25" s="46" t="n">
+        <v>5175</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>Vin Cubi Jura tradition</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="n">
+        <v>390</v>
+      </c>
+      <c r="F26" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H26" s="46" t="n">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B27" s="46" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C27" s="46" t="inlineStr">
+        <is>
+          <t>Sirop dilué</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E27" s="46" t="n">
+        <v>634</v>
+      </c>
+      <c r="F27" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="46" t="n">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="inlineStr">
+        <is>
+          <t>Jus de pomme Saveur de la Ferme</t>
+        </is>
+      </c>
+      <c r="D28" s="46" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E28" s="46" t="n">
+        <v>317</v>
+      </c>
+      <c r="F28" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="46" t="n">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B29" s="46" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="inlineStr">
+        <is>
+          <t>Mortuacienne (limonade)</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E29" s="46" t="n">
+        <v>127</v>
+      </c>
+      <c r="F29" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="46" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B30" s="46" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C30" s="46" t="inlineStr">
+        <is>
+          <t>Eau pétillante Bisontine</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="inlineStr">
+        <is>
+          <t>Btl verre 1 L</t>
+        </is>
+      </c>
+      <c r="E30" s="46" t="n">
+        <v>32</v>
+      </c>
+      <c r="F30" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="46" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>Eau plate (BFC)</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>Btl verre 1 L</t>
+        </is>
+      </c>
+      <c r="E31" s="46" t="n">
+        <v>32</v>
+      </c>
+      <c r="F31" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="46" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C32" s="46" t="inlineStr">
+        <is>
+          <t>Café moulu équitable BFC</t>
+        </is>
+      </c>
+      <c r="D32" s="46" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E32" s="46" t="n">
+        <v>240</v>
+      </c>
+      <c r="F32" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="46" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C33" s="46" t="inlineStr">
+        <is>
+          <t>Pop-corn</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="inlineStr">
+        <is>
+          <t>Gobelet 72 cL</t>
+        </is>
+      </c>
+      <c r="E33" s="46" t="n">
+        <v>285</v>
+      </c>
+      <c r="F33" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="46" t="n">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C34" s="46" t="inlineStr">
+        <is>
+          <t>Frites (snack à part)</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="inlineStr">
+        <is>
+          <t>Barquette kraft 150 g</t>
+        </is>
+      </c>
+      <c r="E34" s="46" t="n">
+        <v>240</v>
+      </c>
+      <c r="F34" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" s="46" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B35" s="46" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C35" s="46" t="inlineStr">
+        <is>
+          <t>Glace 1 boule</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="inlineStr">
+        <is>
+          <t>Cornet gaufrette</t>
+        </is>
+      </c>
+      <c r="E35" s="46" t="n">
+        <v>243</v>
+      </c>
+      <c r="F35" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H35" s="46" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B36" s="46" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C36" s="46" t="inlineStr">
+        <is>
+          <t>Glace 2 boules</t>
+        </is>
+      </c>
+      <c r="D36" s="46" t="inlineStr">
+        <is>
+          <t>Cornet gaufrette</t>
+        </is>
+      </c>
+      <c r="E36" s="46" t="n">
+        <v>162</v>
+      </c>
+      <c r="F36" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="46" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C37" s="46" t="inlineStr">
+        <is>
+          <t>Tomates cerise BRUNO</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="inlineStr">
+        <is>
+          <t>Gobelet 25 cL (150 g)</t>
+        </is>
+      </c>
+      <c r="E37" s="46" t="n">
+        <v>290</v>
+      </c>
+      <c r="F37" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H37" s="46" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B38" s="46" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C38" s="46" t="inlineStr">
+        <is>
+          <t>Petite assiette franc-comtoise</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="E38" s="46" t="n">
+        <v>137</v>
+      </c>
+      <c r="F38" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="H38" s="46" t="n">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B39" s="46" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C39" s="46" t="inlineStr">
+        <is>
+          <t>Petite assiette végétarienne</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="E39" s="46" t="n">
+        <v>57</v>
+      </c>
+      <c r="F39" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="H39" s="46" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B40" s="46" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C40" s="46" t="inlineStr">
+        <is>
+          <t>Grande assiette franc-comtoise</t>
+        </is>
+      </c>
+      <c r="D40" s="46" t="inlineStr">
+        <is>
+          <t>Plateau + frites</t>
+        </is>
+      </c>
+      <c r="E40" s="46" t="n">
+        <v>319</v>
+      </c>
+      <c r="F40" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="H40" s="46" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B41" s="46" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C41" s="46" t="inlineStr">
+        <is>
+          <t>Grande assiette végétarienne</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="inlineStr">
+        <is>
+          <t>Plateau + frites</t>
+        </is>
+      </c>
+      <c r="E41" s="46" t="n">
+        <v>137</v>
+      </c>
+      <c r="F41" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="H41" s="46" t="n">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="46" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B42" s="46" t="inlineStr">
+        <is>
+          <t>Consommables</t>
+        </is>
+      </c>
+      <c r="C42" s="46" t="inlineStr">
+        <is>
+          <t>Consigne écocup non remboursée</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="inlineStr">
+        <is>
+          <t>Jeton</t>
+        </is>
+      </c>
+      <c r="E42" s="46" t="n">
+        <v>118</v>
+      </c>
+      <c r="F42" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H42" s="46" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total Samedi</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="30" t="n"/>
+      <c r="F43" s="30" t="n"/>
+      <c r="G43" s="30" t="n"/>
+      <c r="H43" s="30">
+        <f>SUM(H25:H42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B44" s="47" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C44" s="47" t="inlineStr">
+        <is>
+          <t>Bière blonde/blanche Le Pintadier</t>
+        </is>
+      </c>
+      <c r="D44" s="47" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E44" s="47" t="n">
+        <v>150</v>
+      </c>
+      <c r="F44" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H44" s="47" t="n">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B45" s="47" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C45" s="47" t="inlineStr">
+        <is>
+          <t>Vin Cubi Jura tradition</t>
+        </is>
+      </c>
+      <c r="D45" s="47" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E45" s="47" t="n">
+        <v>68</v>
+      </c>
+      <c r="F45" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H45" s="47" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B46" s="47" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C46" s="47" t="inlineStr">
+        <is>
+          <t>Sirop dilué</t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E46" s="47" t="n">
+        <v>219</v>
+      </c>
+      <c r="F46" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" s="47" t="n">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B47" s="47" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C47" s="47" t="inlineStr">
+        <is>
+          <t>Jus de pomme Saveur de la Ferme</t>
+        </is>
+      </c>
+      <c r="D47" s="47" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E47" s="47" t="n">
+        <v>110</v>
+      </c>
+      <c r="F47" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="47" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B48" s="47" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C48" s="47" t="inlineStr">
+        <is>
+          <t>Mortuacienne (limonade)</t>
+        </is>
+      </c>
+      <c r="D48" s="47" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E48" s="47" t="n">
+        <v>44</v>
+      </c>
+      <c r="F48" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="47" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B49" s="47" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C49" s="47" t="inlineStr">
+        <is>
+          <t>Eau pétillante Bisontine</t>
+        </is>
+      </c>
+      <c r="D49" s="47" t="inlineStr">
+        <is>
+          <t>Btl verre 1 L</t>
+        </is>
+      </c>
+      <c r="E49" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="F49" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="47" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B50" s="47" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C50" s="47" t="inlineStr">
+        <is>
+          <t>Eau plate (BFC)</t>
+        </is>
+      </c>
+      <c r="D50" s="47" t="inlineStr">
+        <is>
+          <t>Btl verre 1 L</t>
+        </is>
+      </c>
+      <c r="E50" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="F50" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" s="47" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B51" s="47" t="inlineStr">
+        <is>
+          <t>Buvette</t>
+        </is>
+      </c>
+      <c r="C51" s="47" t="inlineStr">
+        <is>
+          <t>Café moulu équitable BFC</t>
+        </is>
+      </c>
+      <c r="D51" s="47" t="inlineStr">
+        <is>
+          <t>Verre 25 cL</t>
+        </is>
+      </c>
+      <c r="E51" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="F51" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H51" s="47" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B52" s="47" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C52" s="47" t="inlineStr">
+        <is>
+          <t>Pop-corn</t>
+        </is>
+      </c>
+      <c r="D52" s="47" t="inlineStr">
+        <is>
+          <t>Gobelet 72 cL</t>
+        </is>
+      </c>
+      <c r="E52" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="F52" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H52" s="47" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B53" s="47" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C53" s="47" t="inlineStr">
+        <is>
+          <t>Frites (snack à part)</t>
+        </is>
+      </c>
+      <c r="D53" s="47" t="inlineStr">
+        <is>
+          <t>Barquette kraft 150 g</t>
+        </is>
+      </c>
+      <c r="E53" s="47" t="n">
+        <v>80</v>
+      </c>
+      <c r="F53" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="47" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B54" s="47" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C54" s="47" t="inlineStr">
+        <is>
+          <t>Glace 1 boule</t>
+        </is>
+      </c>
+      <c r="D54" s="47" t="inlineStr">
+        <is>
+          <t>Cornet gaufrette</t>
+        </is>
+      </c>
+      <c r="E54" s="47" t="n">
+        <v>62</v>
+      </c>
+      <c r="F54" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H54" s="47" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B55" s="47" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C55" s="47" t="inlineStr">
+        <is>
+          <t>Glace 2 boules</t>
+        </is>
+      </c>
+      <c r="D55" s="47" t="inlineStr">
+        <is>
+          <t>Cornet gaufrette</t>
+        </is>
+      </c>
+      <c r="E55" s="47" t="n">
+        <v>41</v>
+      </c>
+      <c r="F55" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="47" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B56" s="47" t="inlineStr">
+        <is>
+          <t>Snacks</t>
+        </is>
+      </c>
+      <c r="C56" s="47" t="inlineStr">
+        <is>
+          <t>Tomates cerise BRUNO</t>
+        </is>
+      </c>
+      <c r="D56" s="47" t="inlineStr">
+        <is>
+          <t>Gobelet 25 cL (150 g)</t>
+        </is>
+      </c>
+      <c r="E56" s="47" t="n">
+        <v>110</v>
+      </c>
+      <c r="F56" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H56" s="47" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B57" s="47" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C57" s="47" t="inlineStr">
+        <is>
+          <t>Petite assiette franc-comtoise</t>
+        </is>
+      </c>
+      <c r="D57" s="47" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="E57" s="47" t="n">
+        <v>47</v>
+      </c>
+      <c r="F57" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="G57" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="H57" s="47" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B58" s="47" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C58" s="47" t="inlineStr">
+        <is>
+          <t>Petite assiette végétarienne</t>
+        </is>
+      </c>
+      <c r="D58" s="47" t="inlineStr">
+        <is>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="E58" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="F58" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="G58" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="H58" s="47" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B59" s="47" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C59" s="47" t="inlineStr">
+        <is>
+          <t>Grande assiette franc-comtoise</t>
+        </is>
+      </c>
+      <c r="D59" s="47" t="inlineStr">
+        <is>
+          <t>Plateau + frites</t>
+        </is>
+      </c>
+      <c r="E59" s="47" t="n">
+        <v>110</v>
+      </c>
+      <c r="F59" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G59" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="H59" s="47" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B60" s="47" t="inlineStr">
+        <is>
+          <t>Restauration</t>
+        </is>
+      </c>
+      <c r="C60" s="47" t="inlineStr">
+        <is>
+          <t>Grande assiette végétarienne</t>
+        </is>
+      </c>
+      <c r="D60" s="47" t="inlineStr">
+        <is>
+          <t>Plateau + frites</t>
+        </is>
+      </c>
+      <c r="E60" s="47" t="n">
+        <v>47</v>
+      </c>
+      <c r="F60" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G60" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="H60" s="47" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="47" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B61" s="47" t="inlineStr">
+        <is>
+          <t>Consommables</t>
+        </is>
+      </c>
+      <c r="C61" s="47" t="inlineStr">
+        <is>
+          <t>Consigne écocup non remboursée</t>
+        </is>
+      </c>
+      <c r="D61" s="47" t="inlineStr">
+        <is>
+          <t>Jeton</t>
+        </is>
+      </c>
+      <c r="E61" s="47" t="n">
+        <v>41</v>
+      </c>
+      <c r="F61" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H61" s="47" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total Dimanche</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="n"/>
+      <c r="C62" s="30" t="n"/>
+      <c r="D62" s="30" t="n"/>
+      <c r="E62" s="30" t="n"/>
+      <c r="F62" s="30" t="n"/>
+      <c r="G62" s="30" t="n"/>
+      <c r="H62" s="30">
+        <f>SUM(H44:H61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL RECETTES F&amp;B</t>
+        </is>
+      </c>
+      <c r="B63" s="48" t="n"/>
+      <c r="C63" s="48" t="n"/>
+      <c r="D63" s="48" t="n"/>
+      <c r="E63" s="48" t="n"/>
+      <c r="F63" s="48" t="n"/>
+      <c r="G63" s="48" t="n"/>
+      <c r="H63" s="48">
+        <f>SUM(H6:H62)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="33" t="inlineStr">
+        <is>
+          <t>DÉPENSES — Détail par achat (achat unique, distinction Type / Catégorie / Mois)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Mois</t>
+        </is>
+      </c>
+      <c r="B67" s="28" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
-        <is>
-          <t>Prévu</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>Réel</t>
-        </is>
-      </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>Écart</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="n"/>
-      <c r="B6" s="29" t="inlineStr">
-        <is>
-          <t>Buvette Vendredi : bière 1200 + vin 540 + soft 793 + café 81</t>
-        </is>
-      </c>
-      <c r="C6" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>2614</v>
-      </c>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="29">
-        <f>E6-D6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="29" t="n"/>
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>Buvette Samedi : bière 4600 + vin 1950 + soft 3439 + café 477 (jour fort)</t>
-        </is>
-      </c>
-      <c r="C7" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D7" s="29" t="n">
-        <v>10466</v>
-      </c>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="29">
-        <f>E7-D7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="29" t="n"/>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>Buvette Dimanche : bière 600 + vin 340 + soft 1188 + café 162</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D8" s="29" t="n">
-        <v>2290</v>
-      </c>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29">
-        <f>E8-D8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>Restauration repas Vendredi : 225 assiettes (70% Grande 12€ / 30% Petite 9€, FC ou végé)</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>2498</v>
-      </c>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29">
-        <f>E9-D9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="n"/>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>Restauration repas Samedi : 650 assiettes (Petite 9€ / Grande 12€, FC ou végé)</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>7215</v>
-      </c>
-      <c r="E10" s="29" t="n"/>
-      <c r="F10" s="29">
-        <f>E10-D10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29" t="n"/>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>Restauration repas Dimanche : 225 assiettes (Petite 9€ / Grande 12€, FC ou végé)</t>
-        </is>
-      </c>
-      <c r="C11" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>2498</v>
-      </c>
-      <c r="E11" s="29" t="n"/>
-      <c r="F11" s="29">
-        <f>E11-D11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="n"/>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>Snacks Vendredi : pop-corn 60 (40p × 1,50€) + frites 120 + glaces 109 + tomates 150 (100p × 1,50€)</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>439</v>
-      </c>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="29">
-        <f>E12-D12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="n"/>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>Snacks Samedi : pop-corn 428 (285p × 1,50€) + frites 705 + glaces 850 + tomates 435 (290p × 1,50€)</t>
-        </is>
-      </c>
-      <c r="C13" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>2418</v>
-      </c>
-      <c r="E13" s="29" t="n"/>
-      <c r="F13" s="29">
-        <f>E13-D13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="n"/>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>Snacks Dimanche : pop-corn 120 (80p × 1,50€) + frites 240 + glaces 218 + tomates 165 (110p × 1,50€)</t>
-        </is>
-      </c>
-      <c r="C14" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>743</v>
-      </c>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29">
-        <f>E14-D14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="29" t="n"/>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>Consignes écocup non remboursées (1 000 écocups × 20 % non-retour × 1 €)</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>Recette</t>
-        </is>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>200</v>
-      </c>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29">
-        <f>E15-D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="D67" s="28" t="inlineStr">
+        <is>
+          <t>Produit / Achat</t>
+        </is>
+      </c>
+      <c r="E67" s="28" t="inlineStr">
+        <is>
+          <t>Quantité</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="G67" s="28" t="inlineStr">
+        <is>
+          <t>Prix unit €</t>
+        </is>
+      </c>
+      <c r="H67" s="28" t="inlineStr">
+        <is>
+          <t>Coût total €</t>
+        </is>
+      </c>
+      <c r="I67" s="28" t="inlineStr">
+        <is>
+          <t>Fournisseur</t>
+        </is>
+      </c>
+      <c r="J67" s="28" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="49" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B68" s="49" t="inlineStr">
+        <is>
+          <t>Invest</t>
+        </is>
+      </c>
+      <c r="C68" s="49" t="inlineStr">
+        <is>
+          <t>Vaisselle réutilisable</t>
+        </is>
+      </c>
+      <c r="D68" s="49" t="inlineStr">
+        <is>
+          <t>Écocups réutilisables PP 25 cL</t>
+        </is>
+      </c>
+      <c r="E68" s="49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F68" s="49" t="inlineStr">
+        <is>
+          <t>unités</t>
+        </is>
+      </c>
+      <c r="G68" s="49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H68" s="49" t="n">
+        <v>600</v>
+      </c>
+      <c r="I68" s="49" t="inlineStr">
+        <is>
+          <t>Atomic</t>
+        </is>
+      </c>
+      <c r="J68" s="49" t="inlineStr">
+        <is>
+          <t>Délai livraison ~3 sem · réutilisable édition 2027+</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="49" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B69" s="49" t="inlineStr">
+        <is>
+          <t>Invest</t>
+        </is>
+      </c>
+      <c r="C69" s="49" t="inlineStr">
+        <is>
+          <t>Caisse / paiement</t>
+        </is>
+      </c>
+      <c r="D69" s="49" t="inlineStr">
+        <is>
+          <t>Jetons flousy ~5000 unités (mix 1/2/5/10)</t>
+        </is>
+      </c>
+      <c r="E69" s="49" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F69" s="49" t="inlineStr">
+        <is>
+          <t>unités</t>
+        </is>
+      </c>
+      <c r="G69" s="49" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H69" s="49" t="n">
+        <v>400</v>
+      </c>
+      <c r="I69" s="49" t="inlineStr">
+        <is>
+          <t>jeton-monnaie.fr ou gravoplaque.com</t>
+        </is>
+      </c>
+      <c r="J69" s="49" t="inlineStr">
+        <is>
+          <t>{1×2000, 2×1000, 5×1500, 10×500}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="50" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B70" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C70" s="50" t="inlineStr">
+        <is>
+          <t>Équipement loué</t>
+        </is>
+      </c>
+      <c r="D70" s="50" t="inlineStr">
+        <is>
+          <t>Acompte 30% machine pop-corn (location)</t>
+        </is>
+      </c>
+      <c r="E70" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="50" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="G70" s="50" t="n">
+        <v>80</v>
+      </c>
+      <c r="H70" s="50" t="n">
+        <v>80</v>
+      </c>
+      <c r="I70" s="50" t="inlineStr">
+        <is>
+          <t>À finaliser</t>
+        </is>
+      </c>
+      <c r="J70" s="50" t="inlineStr">
+        <is>
+          <t>Solde 172 € en août</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="50" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B71" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C71" s="50" t="inlineStr">
+        <is>
+          <t>HACCP</t>
+        </is>
+      </c>
+      <c r="D71" s="50" t="inlineStr">
+        <is>
+          <t>Tablier + charlotte + gants jetables + sonde T° + désinfectant</t>
+        </is>
+      </c>
+      <c r="E71" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="50" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="G71" s="50" t="n">
+        <v>80</v>
+      </c>
+      <c r="H71" s="50" t="n">
+        <v>80</v>
+      </c>
+      <c r="I71" s="50" t="inlineStr">
+        <is>
+          <t>Metro / fournisseur HoReCa</t>
+        </is>
+      </c>
+      <c r="J71" s="50" t="inlineStr">
+        <is>
+          <t>Obligation cuisson frites</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="50" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B72" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C72" s="50" t="inlineStr">
+        <is>
+          <t>Caisse / Admin</t>
+        </is>
+      </c>
+      <c r="D72" s="50" t="inlineStr">
+        <is>
+          <t>Caisse + fond de caisse 300 € + ustensiles préparation</t>
+        </is>
+      </c>
+      <c r="E72" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="50" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="G72" s="50" t="n">
+        <v>280</v>
+      </c>
+      <c r="H72" s="50" t="n">
+        <v>280</v>
+      </c>
+      <c r="I72" s="50" t="inlineStr">
+        <is>
+          <t>Divers</t>
+        </is>
+      </c>
+      <c r="J72" s="50" t="inlineStr">
+        <is>
+          <t>Espèces + planche + couteaux + plateaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="50" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B73" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C73" s="50" t="inlineStr">
+        <is>
+          <t>HACCP</t>
+        </is>
+      </c>
+      <c r="D73" s="50" t="inlineStr">
+        <is>
+          <t>Trousse premiers secours buvette</t>
+        </is>
+      </c>
+      <c r="E73" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="50" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="G73" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="H73" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="50" t="inlineStr">
+        <is>
+          <t>Pharmacie</t>
+        </is>
+      </c>
+      <c r="J73" s="50" t="inlineStr">
+        <is>
+          <t>Obligation</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="50" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B74" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C74" s="50" t="inlineStr">
+        <is>
+          <t>Caisse / Admin</t>
+        </is>
+      </c>
+      <c r="D74" s="50" t="inlineStr">
+        <is>
+          <t>Affichage prix (ardoises grand format + marqueurs)</t>
+        </is>
+      </c>
+      <c r="E74" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="50" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="G74" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="H74" s="50" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="50" t="inlineStr">
+        <is>
+          <t>Cultura / Bureau Vallée</t>
+        </is>
+      </c>
+      <c r="J74" s="50" t="inlineStr">
+        <is>
+          <t>Bar + Restauration + allergènes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="50" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B75" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C75" s="50" t="inlineStr">
+        <is>
+          <t>HACCP</t>
+        </is>
+      </c>
+      <c r="D75" s="50" t="inlineStr">
+        <is>
+          <t>Sacs poubelles tri (verre/biodéchets/OMR) + bidon huile usagée</t>
+        </is>
+      </c>
+      <c r="E75" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="50" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="G75" s="50" t="n">
+        <v>70</v>
+      </c>
+      <c r="H75" s="50" t="n">
+        <v>70</v>
+      </c>
+      <c r="I75" s="50" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="J75" s="50" t="inlineStr">
+        <is>
+          <t>Tri sélectif charte éthique</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="50" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B76" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C76" s="50" t="inlineStr">
+        <is>
+          <t>Vaisselle bio jetable</t>
+        </is>
+      </c>
+      <c r="D76" s="50" t="inlineStr">
+        <is>
+          <t>Vaisselle bio jetable globale (gobelets + assiettes + cuillères + serviettes + barquettes)</t>
+        </is>
+      </c>
+      <c r="E76" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="50" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="G76" s="50" t="n">
+        <v>319</v>
+      </c>
+      <c r="H76" s="50" t="n">
+        <v>319</v>
+      </c>
+      <c r="I76" s="50" t="inlineStr">
+        <is>
+          <t>Cdiscount Pro / Vegware</t>
+        </is>
+      </c>
+      <c r="J76" s="50" t="inlineStr">
+        <is>
+          <t>Détail composition voir Calibrage_buvette_2026.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="50" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B77" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C77" s="50" t="inlineStr">
+        <is>
+          <t>Équipement loué</t>
+        </is>
+      </c>
+      <c r="D77" s="50" t="inlineStr">
+        <is>
+          <t>Solde 70% machine pop-corn</t>
+        </is>
+      </c>
+      <c r="E77" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="50" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="G77" s="50" t="n">
+        <v>172</v>
+      </c>
+      <c r="H77" s="50" t="n">
+        <v>172</v>
+      </c>
+      <c r="I77" s="50" t="inlineStr">
+        <is>
+          <t>À finaliser</t>
+        </is>
+      </c>
+      <c r="J77" s="50" t="inlineStr">
+        <is>
+          <t>Au montage J-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="50" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B78" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C78" s="50" t="inlineStr">
+        <is>
+          <t>Équipement loué</t>
+        </is>
+      </c>
+      <c r="D78" s="50" t="inlineStr">
+        <is>
+          <t>Percolateurs 4 × 10 L</t>
+        </is>
+      </c>
+      <c r="E78" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F78" s="50" t="inlineStr">
+        <is>
+          <t>unités</t>
+        </is>
+      </c>
+      <c r="G78" s="50" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="H78" s="50" t="n">
+        <v>345</v>
+      </c>
+      <c r="I78" s="50" t="inlineStr">
+        <is>
+          <t>ABC LOCATION</t>
+        </is>
+      </c>
+      <c r="J78" s="50" t="inlineStr">
+        <is>
+          <t>Capacité 320 cafés/tournée</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="50" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B79" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C79" s="50" t="inlineStr">
+        <is>
+          <t>Équipement loué</t>
+        </is>
+      </c>
+      <c r="D79" s="50" t="inlineStr">
+        <is>
+          <t>Friteuses pro × 2</t>
+        </is>
+      </c>
+      <c r="E79" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="50" t="inlineStr">
+        <is>
+          <t>unités</t>
+        </is>
+      </c>
+      <c r="G79" s="50" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="H79" s="50" t="n">
+        <v>172</v>
+      </c>
+      <c r="I79" s="50" t="inlineStr">
+        <is>
+          <t>ABC LOCATION</t>
+        </is>
+      </c>
+      <c r="J79" s="50" t="inlineStr">
+        <is>
+          <t>~2-3 tournées/heure samedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="50" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B80" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C80" s="50" t="inlineStr">
+        <is>
+          <t>Équipement loué</t>
+        </is>
+      </c>
+      <c r="D80" s="50" t="inlineStr">
+        <is>
+          <t>Eau gratuite : 2-3 fontaines + carafes/pichets</t>
+        </is>
+      </c>
+      <c r="E80" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="50" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="G80" s="50" t="n">
+        <v>400</v>
+      </c>
+      <c r="H80" s="50" t="n">
+        <v>400</v>
+      </c>
+      <c r="I80" s="50" t="inlineStr">
+        <is>
+          <t>Loca-Buffet / Loxam / Kiloutou</t>
+        </is>
+      </c>
+      <c r="J80" s="50" t="inlineStr">
+        <is>
+          <t>Charte éthique + obligation bénévoles</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="50" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B81" s="50" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+      <c r="C81" s="50" t="inlineStr">
+        <is>
+          <t>HACCP</t>
+        </is>
+      </c>
+      <c r="D81" s="50" t="inlineStr">
+        <is>
+          <t>Lavage écocups (produit vaisselle pro + brosses + éponges)</t>
+        </is>
+      </c>
+      <c r="E81" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="50" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="G81" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="H81" s="50" t="n">
+        <v>50</v>
+      </c>
+      <c r="I81" s="50" t="inlineStr">
+        <is>
+          <t>Metro / fournisseur HoReCa</t>
+        </is>
+      </c>
+      <c r="J81" s="50" t="inlineStr">
+        <is>
+          <t>Stand rinçage rapide près du bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B82" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C82" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Bière</t>
+        </is>
+      </c>
+      <c r="D82" s="51" t="inlineStr">
+        <is>
+          <t>Bière blonde+blanche fûts 40 L (commande initiale ferme)</t>
+        </is>
+      </c>
+      <c r="E82" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" s="51" t="inlineStr">
+        <is>
+          <t>fûts</t>
+        </is>
+      </c>
+      <c r="G82" s="51" t="n">
+        <v>80</v>
+      </c>
+      <c r="H82" s="51" t="n">
+        <v>800</v>
+      </c>
+      <c r="I82" s="51" t="inlineStr">
+        <is>
+          <t>Le Pintadier</t>
+        </is>
+      </c>
+      <c r="J82" s="51" t="inlineStr">
+        <is>
+          <t>1600 verres · réassort 5 fûts décision Ven soir</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B83" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Vin</t>
+        </is>
+      </c>
+      <c r="D83" s="51" t="inlineStr">
+        <is>
+          <t>Vin Cubi Jura tradition 5 L (prix négocié)</t>
+        </is>
+      </c>
+      <c r="E83" s="51" t="n">
+        <v>29</v>
+      </c>
+      <c r="F83" s="51" t="inlineStr">
+        <is>
+          <t>cubis</t>
+        </is>
+      </c>
+      <c r="G83" s="51" t="n">
+        <v>50</v>
+      </c>
+      <c r="H83" s="51" t="n">
+        <v>1450</v>
+      </c>
+      <c r="I83" s="51" t="inlineStr">
+        <is>
+          <t>Hyper Boisson</t>
+        </is>
+      </c>
+      <c r="J83" s="51" t="inlineStr">
+        <is>
+          <t>580 verres · prix à confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B84" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C84" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Soft</t>
+        </is>
+      </c>
+      <c r="D84" s="51" t="inlineStr">
+        <is>
+          <t>Sirop dilué (parfums grenadine/menthe/citron à préciser)</t>
+        </is>
+      </c>
+      <c r="E84" s="51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F84" s="51" t="inlineStr">
+        <is>
+          <t>L (estim.)</t>
+        </is>
+      </c>
+      <c r="G84" s="51" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H84" s="51" t="n">
+        <v>300</v>
+      </c>
+      <c r="I84" s="51" t="inlineStr">
+        <is>
+          <t>Hyper Boisson</t>
+        </is>
+      </c>
+      <c r="J84" s="51" t="inlineStr">
+        <is>
+          <t>1000 verres dilués</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B85" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C85" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Soft</t>
+        </is>
+      </c>
+      <c r="D85" s="51" t="inlineStr">
+        <is>
+          <t>Jus de pomme local poche 3 L</t>
+        </is>
+      </c>
+      <c r="E85" s="51" t="n">
+        <v>21</v>
+      </c>
+      <c r="F85" s="51" t="inlineStr">
+        <is>
+          <t>poches</t>
+        </is>
+      </c>
+      <c r="G85" s="51" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H85" s="51" t="n">
+        <v>176</v>
+      </c>
+      <c r="I85" s="51" t="inlineStr">
+        <is>
+          <t>Saveur de la Ferme</t>
+        </is>
+      </c>
+      <c r="J85" s="51" t="inlineStr">
+        <is>
+          <t>Pour 500 verres (à recouper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B86" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C86" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Soft</t>
+        </is>
+      </c>
+      <c r="D86" s="51" t="inlineStr">
+        <is>
+          <t>Mortuacienne btl verre 1 L (vendue au verre)</t>
+        </is>
+      </c>
+      <c r="E86" s="51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" s="51" t="inlineStr">
+        <is>
+          <t>btl</t>
+        </is>
+      </c>
+      <c r="G86" s="51" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H86" s="51" t="n">
+        <v>58</v>
+      </c>
+      <c r="I86" s="51" t="inlineStr">
+        <is>
+          <t>Hyper Boisson</t>
+        </is>
+      </c>
+      <c r="J86" s="51" t="inlineStr">
+        <is>
+          <t>200 verres</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C87" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Soft</t>
+        </is>
+      </c>
+      <c r="D87" s="51" t="inlineStr">
+        <is>
+          <t>Eau pétillante Bisontine btl verre 1 L</t>
+        </is>
+      </c>
+      <c r="E87" s="51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F87" s="51" t="inlineStr">
+        <is>
+          <t>btl</t>
+        </is>
+      </c>
+      <c r="G87" s="51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H87" s="51" t="n">
+        <v>35</v>
+      </c>
+      <c r="I87" s="51" t="inlineStr">
+        <is>
+          <t>Hyper Boisson</t>
+        </is>
+      </c>
+      <c r="J87" s="51" t="inlineStr">
+        <is>
+          <t>Vendue entière + consigne 1 fl</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C88" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Soft</t>
+        </is>
+      </c>
+      <c r="D88" s="51" t="inlineStr">
+        <is>
+          <t>Eau plate btl verre 1 L (à sourcer)</t>
+        </is>
+      </c>
+      <c r="E88" s="51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F88" s="51" t="inlineStr">
+        <is>
+          <t>btl</t>
+        </is>
+      </c>
+      <c r="G88" s="51" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H88" s="51" t="n">
+        <v>32</v>
+      </c>
+      <c r="I88" s="51" t="inlineStr">
+        <is>
+          <t>Velleminfroy / Saint-Antonin (à confirmer)</t>
+        </is>
+      </c>
+      <c r="J88" s="51" t="inlineStr">
+        <is>
+          <t>Vendue entière + consigne 1 fl</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B89" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C89" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Café</t>
+        </is>
+      </c>
+      <c r="D89" s="51" t="inlineStr">
+        <is>
+          <t>Café moulu équitable BFC</t>
+        </is>
+      </c>
+      <c r="E89" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" s="51" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G89" s="51" t="n">
+        <v>15</v>
+      </c>
+      <c r="H89" s="51" t="n">
+        <v>45</v>
+      </c>
+      <c r="I89" s="51" t="inlineStr">
+        <is>
+          <t>Torréfacteur BFC à sourcer</t>
+        </is>
+      </c>
+      <c r="J89" s="51" t="inlineStr">
+        <is>
+          <t>7 g/tasse, 360 cafés</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B90" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C90" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Café</t>
+        </is>
+      </c>
+      <c r="D90" s="51" t="inlineStr">
+        <is>
+          <t>Sucre sticks</t>
+        </is>
+      </c>
+      <c r="E90" s="51" t="n">
+        <v>360</v>
+      </c>
+      <c r="F90" s="51" t="inlineStr">
+        <is>
+          <t>sticks</t>
+        </is>
+      </c>
+      <c r="G90" s="51" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H90" s="51" t="n">
+        <v>11</v>
+      </c>
+      <c r="I90" s="51" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="J90" s="51" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B91" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C91" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Café</t>
+        </is>
+      </c>
+      <c r="D91" s="51" t="inlineStr">
+        <is>
+          <t>Lait UHT mini-portions</t>
+        </is>
+      </c>
+      <c r="E91" s="51" t="n">
+        <v>250</v>
+      </c>
+      <c r="F91" s="51" t="inlineStr">
+        <is>
+          <t>portions</t>
+        </is>
+      </c>
+      <c r="G91" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H91" s="51" t="n">
+        <v>25</v>
+      </c>
+      <c r="I91" s="51" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="J91" s="51" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B92" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C92" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Café</t>
+        </is>
+      </c>
+      <c r="D92" s="51" t="inlineStr">
+        <is>
+          <t>Mélangeurs bois</t>
+        </is>
+      </c>
+      <c r="E92" s="51" t="n">
+        <v>360</v>
+      </c>
+      <c r="F92" s="51" t="inlineStr">
+        <is>
+          <t>unités</t>
+        </is>
+      </c>
+      <c r="G92" s="51" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H92" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="I92" s="51" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="J92" s="51" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B93" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C93" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Bar</t>
+        </is>
+      </c>
+      <c r="D93" s="51" t="inlineStr">
+        <is>
+          <t>Sucre bar additionnel + glace pilée bar</t>
+        </is>
+      </c>
+      <c r="E93" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="51" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="G93" s="51" t="n">
+        <v>60</v>
+      </c>
+      <c r="H93" s="51" t="n">
+        <v>60</v>
+      </c>
+      <c r="I93" s="51" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="J93" s="51" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B94" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C94" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Pop-corn</t>
+        </is>
+      </c>
+      <c r="D94" s="51" t="inlineStr">
+        <is>
+          <t>Maïs pop-corn</t>
+        </is>
+      </c>
+      <c r="E94" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" s="51" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G94" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H94" s="51" t="n">
+        <v>15</v>
+      </c>
+      <c r="I94" s="51" t="inlineStr">
+        <is>
+          <t>Metro / grossiste</t>
+        </is>
+      </c>
+      <c r="J94" s="51" t="inlineStr">
+        <is>
+          <t>405 portions</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B95" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C95" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Pop-corn</t>
+        </is>
+      </c>
+      <c r="D95" s="51" t="inlineStr">
+        <is>
+          <t>Huile + sel pop-corn</t>
+        </is>
+      </c>
+      <c r="E95" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="51" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="G95" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="H95" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="I95" s="51" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="J95" s="51" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B96" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C96" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Frites</t>
+        </is>
+      </c>
+      <c r="D96" s="51" t="inlineStr">
+        <is>
+          <t>Pommes de terre BFC (frites snack 50 kg + grandes assiettes 110 kg)</t>
+        </is>
+      </c>
+      <c r="E96" s="51" t="n">
+        <v>160</v>
+      </c>
+      <c r="F96" s="51" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G96" s="51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H96" s="51" t="n">
+        <v>192</v>
+      </c>
+      <c r="I96" s="51" t="inlineStr">
+        <is>
+          <t>Producteur BFC à sourcer (Bruno ?)</t>
+        </is>
+      </c>
+      <c r="J96" s="51" t="inlineStr">
+        <is>
+          <t>Total snack + grandes assiettes</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B97" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C97" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Frites</t>
+        </is>
+      </c>
+      <c r="D97" s="51" t="inlineStr">
+        <is>
+          <t>Huile friture</t>
+        </is>
+      </c>
+      <c r="E97" s="51" t="n">
+        <v>18</v>
+      </c>
+      <c r="F97" s="51" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G97" s="51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H97" s="51" t="n">
+        <v>32</v>
+      </c>
+      <c r="I97" s="51" t="inlineStr">
+        <is>
+          <t>Metro / grossiste</t>
+        </is>
+      </c>
+      <c r="J97" s="51" t="inlineStr">
+        <is>
+          <t>Cuisson + renouvellement</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B98" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C98" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Frites</t>
+        </is>
+      </c>
+      <c r="D98" s="51" t="inlineStr">
+        <is>
+          <t>Sel friture</t>
+        </is>
+      </c>
+      <c r="E98" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="51" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="G98" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" s="51" t="inlineStr">
+        <is>
+          <t>Metro</t>
+        </is>
+      </c>
+      <c r="J98" s="51" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B99" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C99" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Frites</t>
+        </is>
+      </c>
+      <c r="D99" s="51" t="inlineStr">
+        <is>
+          <t>Barquettes kraft 150 g (snack à part uniquement)</t>
+        </is>
+      </c>
+      <c r="E99" s="51" t="n">
+        <v>360</v>
+      </c>
+      <c r="F99" s="51" t="inlineStr">
+        <is>
+          <t>unités</t>
+        </is>
+      </c>
+      <c r="G99" s="51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H99" s="51" t="n">
+        <v>18</v>
+      </c>
+      <c r="I99" s="51" t="inlineStr">
+        <is>
+          <t>Cdiscount Pro / Metro</t>
+        </is>
+      </c>
+      <c r="J99" s="51" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B100" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C100" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Frites</t>
+        </is>
+      </c>
+      <c r="D100" s="51" t="inlineStr">
+        <is>
+          <t>Sticks ketchup + mayo</t>
+        </is>
+      </c>
+      <c r="E100" s="51" t="n">
+        <v>720</v>
+      </c>
+      <c r="F100" s="51" t="inlineStr">
+        <is>
+          <t>sticks</t>
+        </is>
+      </c>
+      <c r="G100" s="51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H100" s="51" t="n">
+        <v>36</v>
+      </c>
+      <c r="I100" s="51" t="inlineStr">
+        <is>
+          <t>Metro / fournisseur HoReCa</t>
+        </is>
+      </c>
+      <c r="J100" s="51" t="inlineStr">
+        <is>
+          <t>2 sticks/portion snack</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B101" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C101" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Glaces</t>
+        </is>
+      </c>
+      <c r="D101" s="51" t="inlineStr">
+        <is>
+          <t>Glaces vanille/chocolat/fraise bacs 2,5 L</t>
+        </is>
+      </c>
+      <c r="E101" s="51" t="n">
+        <v>39</v>
+      </c>
+      <c r="F101" s="51" t="inlineStr">
+        <is>
+          <t>bacs</t>
+        </is>
+      </c>
+      <c r="G101" s="51" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H101" s="51" t="n">
+        <v>92</v>
+      </c>
+      <c r="I101" s="51" t="inlineStr">
+        <is>
+          <t>ERHARD</t>
+        </is>
+      </c>
+      <c r="J101" s="51" t="inlineStr">
+        <is>
+          <t>780 boules · à confirmer prix</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B102" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C102" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Glaces</t>
+        </is>
+      </c>
+      <c r="D102" s="51" t="inlineStr">
+        <is>
+          <t>Cornets gaufrette comestibles</t>
+        </is>
+      </c>
+      <c r="E102" s="51" t="n">
+        <v>560</v>
+      </c>
+      <c r="F102" s="51" t="inlineStr">
+        <is>
+          <t>unités</t>
+        </is>
+      </c>
+      <c r="G102" s="51" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H102" s="51" t="n">
+        <v>67</v>
+      </c>
+      <c r="I102" s="51" t="inlineStr">
+        <is>
+          <t>Nicolas Glaces / Metro / HoReCa</t>
+        </is>
+      </c>
+      <c r="J102" s="51" t="inlineStr">
+        <is>
+          <t>Zéro déchet</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B103" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C103" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Glaces</t>
+        </is>
+      </c>
+      <c r="D103" s="51" t="inlineStr">
+        <is>
+          <t>Gobelets bio 25 cL back-up allergiques/enfants</t>
+        </is>
+      </c>
+      <c r="E103" s="51" t="n">
+        <v>50</v>
+      </c>
+      <c r="F103" s="51" t="inlineStr">
+        <is>
+          <t>unités</t>
+        </is>
+      </c>
+      <c r="G103" s="51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H103" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="I103" s="51" t="inlineStr">
+        <is>
+          <t>Cdiscount Pro</t>
+        </is>
+      </c>
+      <c r="J103" s="51" t="inlineStr">
+        <is>
+          <t>+ mini-cuillères bois</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B104" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C104" s="51" t="inlineStr">
+        <is>
+          <t>Snack - Tomates</t>
+        </is>
+      </c>
+      <c r="D104" s="51" t="inlineStr">
+        <is>
+          <t>Tomates cerise BFC</t>
+        </is>
+      </c>
+      <c r="E104" s="51" t="n">
+        <v>75</v>
+      </c>
+      <c r="F104" s="51" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G104" s="51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H104" s="51" t="n">
+        <v>90</v>
+      </c>
+      <c r="I104" s="51" t="inlineStr">
+        <is>
+          <t>BRUNO</t>
+        </is>
+      </c>
+      <c r="J104" s="51" t="inlineStr">
+        <is>
+          <t>500 portions × 150 g</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B105" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C105" s="51" t="inlineStr">
+        <is>
+          <t>Restauration - Fromage</t>
+        </is>
+      </c>
+      <c r="D105" s="51" t="inlineStr">
+        <is>
+          <t>Comté + Comté doux + Morbier (mix 70 kg)</t>
+        </is>
+      </c>
+      <c r="E105" s="51" t="n">
+        <v>70</v>
+      </c>
+      <c r="F105" s="51" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G105" s="51" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H105" s="51" t="n">
+        <v>1015</v>
+      </c>
+      <c r="I105" s="51" t="inlineStr">
+        <is>
+          <t>Hôpitaux Vieux</t>
+        </is>
+      </c>
+      <c r="J105" s="51" t="inlineStr">
+        <is>
+          <t>Mix selon assiettes FC + VG</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B106" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C106" s="51" t="inlineStr">
+        <is>
+          <t>Restauration - Charcuterie</t>
+        </is>
+      </c>
+      <c r="D106" s="51" t="inlineStr">
+        <is>
+          <t>Saucisse paysanne + lard fumé + jambon blanc (~77 kg)</t>
+        </is>
+      </c>
+      <c r="E106" s="51" t="n">
+        <v>77</v>
+      </c>
+      <c r="F106" s="51" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G106" s="51" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H106" s="51" t="n">
+        <v>1194</v>
+      </c>
+      <c r="I106" s="51" t="inlineStr">
+        <is>
+          <t>Ferme Ligny</t>
+        </is>
+      </c>
+      <c r="J106" s="51" t="inlineStr">
+        <is>
+          <t>Pour 770 grandes + 231 petites FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B107" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C107" s="51" t="inlineStr">
+        <is>
+          <t>Restauration - Œufs</t>
+        </is>
+      </c>
+      <c r="D107" s="51" t="inlineStr">
+        <is>
+          <t>Œufs plateau 360</t>
+        </is>
+      </c>
+      <c r="E107" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" s="51" t="inlineStr">
+        <is>
+          <t>plateaux</t>
+        </is>
+      </c>
+      <c r="G107" s="51" t="n">
+        <v>66</v>
+      </c>
+      <c r="H107" s="51" t="n">
+        <v>264</v>
+      </c>
+      <c r="I107" s="51" t="inlineStr">
+        <is>
+          <t>Saveur de la Ferme</t>
+        </is>
+      </c>
+      <c r="J107" s="51" t="inlineStr">
+        <is>
+          <t>1100 œufs nécessaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B108" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C108" s="51" t="inlineStr">
+        <is>
+          <t>Restauration - Pain</t>
+        </is>
+      </c>
+      <c r="D108" s="51" t="inlineStr">
+        <is>
+          <t>Pain 350 g (10 tranches/pain)</t>
+        </is>
+      </c>
+      <c r="E108" s="51" t="n">
+        <v>110</v>
+      </c>
+      <c r="F108" s="51" t="inlineStr">
+        <is>
+          <t>pains</t>
+        </is>
+      </c>
+      <c r="G108" s="51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H108" s="51" t="n">
+        <v>242</v>
+      </c>
+      <c r="I108" s="51" t="inlineStr">
+        <is>
+          <t>La Ronde des Pains</t>
+        </is>
+      </c>
+      <c r="J108" s="51" t="inlineStr">
+        <is>
+          <t>1100 tranches</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B109" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C109" s="51" t="inlineStr">
+        <is>
+          <t>Restauration - Conditionnement</t>
+        </is>
+      </c>
+      <c r="D109" s="51" t="inlineStr">
+        <is>
+          <t>Sachets sous vide (par 3 kg)</t>
+        </is>
+      </c>
+      <c r="E109" s="51" t="n">
+        <v>30</v>
+      </c>
+      <c r="F109" s="51" t="inlineStr">
+        <is>
+          <t>lots de 3kg</t>
+        </is>
+      </c>
+      <c r="G109" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="51" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="51" t="inlineStr">
+        <is>
+          <t>Ferme Ligny</t>
+        </is>
+      </c>
+      <c r="J109" s="51" t="inlineStr">
+        <is>
+          <t>Pour conserver fromage + charcut J-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="51" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B110" s="51" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C110" s="51" t="inlineStr">
+        <is>
+          <t>Boisson - Bière</t>
+        </is>
+      </c>
+      <c r="D110" s="51" t="inlineStr">
+        <is>
+          <t>Réassort éventuel 5 fûts (décision Vendredi soir)</t>
+        </is>
+      </c>
+      <c r="E110" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F110" s="51" t="inlineStr">
+        <is>
+          <t>fûts</t>
+        </is>
+      </c>
+      <c r="G110" s="51" t="n">
+        <v>80</v>
+      </c>
+      <c r="H110" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="51" t="inlineStr">
+        <is>
+          <t>Le Pintadier</t>
+        </is>
+      </c>
+      <c r="J110" s="51" t="inlineStr">
+        <is>
+          <t>Activation conditionnelle - 0 € par défaut</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="52" t="n"/>
+      <c r="B112" s="52" t="inlineStr">
+        <is>
+          <t>Sous-total Fixe</t>
+        </is>
+      </c>
+      <c r="C112" s="52" t="n"/>
+      <c r="D112" s="52" t="n"/>
+      <c r="E112" s="52" t="n"/>
+      <c r="F112" s="52" t="n"/>
+      <c r="G112" s="52" t="n"/>
+      <c r="H112" s="52">
+        <f>SUMIF(B68:B110,"Fixe",H68:H110)</f>
+        <v/>
+      </c>
+      <c r="I112" s="52" t="n"/>
+      <c r="J112" s="52" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="53" t="n"/>
+      <c r="B113" s="53" t="inlineStr">
+        <is>
+          <t>Sous-total Invest</t>
+        </is>
+      </c>
+      <c r="C113" s="53" t="n"/>
+      <c r="D113" s="53" t="n"/>
+      <c r="E113" s="53" t="n"/>
+      <c r="F113" s="53" t="n"/>
+      <c r="G113" s="53" t="n"/>
+      <c r="H113" s="53">
+        <f>SUMIF(B68:B111,"Invest",H68:H111)</f>
+        <v/>
+      </c>
+      <c r="I113" s="53" t="n"/>
+      <c r="J113" s="53" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="54" t="n"/>
+      <c r="B114" s="54" t="inlineStr">
+        <is>
+          <t>Sous-total Variable</t>
+        </is>
+      </c>
+      <c r="C114" s="54" t="n"/>
+      <c r="D114" s="54" t="n"/>
+      <c r="E114" s="54" t="n"/>
+      <c r="F114" s="54" t="n"/>
+      <c r="G114" s="54" t="n"/>
+      <c r="H114" s="54">
+        <f>SUMIF(B68:B112,"Variable",H68:H112)</f>
+        <v/>
+      </c>
+      <c r="I114" s="54" t="n"/>
+      <c r="J114" s="54" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="42" t="inlineStr">
+        <is>
+          <t>TOTAL DÉPENSES F&amp;B</t>
+        </is>
+      </c>
+      <c r="B115" s="42" t="n"/>
+      <c r="C115" s="42" t="n"/>
+      <c r="D115" s="42" t="n"/>
+      <c r="E115" s="42" t="n"/>
+      <c r="F115" s="42" t="n"/>
+      <c r="G115" s="42" t="n"/>
+      <c r="H115" s="42">
+        <f>SUM(H68:H110)</f>
+        <v/>
+      </c>
+      <c r="I115" s="42" t="n"/>
+      <c r="J115" s="42" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="34" t="inlineStr">
+        <is>
+          <t>SYNTHÈSE F&amp;B</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="30" t="inlineStr">
         <is>
           <t>TOTAL RECETTES F&amp;B</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n"/>
-      <c r="C16" s="30" t="n"/>
-      <c r="D16" s="30">
-        <f>SUM(D6:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="30">
-        <f>SUM(E6:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="30">
-        <f>E16-D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>COÛTS FIXES (incompressibles — indépendants de la fréquentation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C20" s="28" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D20" s="28" t="inlineStr">
-        <is>
-          <t>Prévu</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="inlineStr">
-        <is>
-          <t>Réel</t>
-        </is>
-      </c>
-      <c r="F20" s="28" t="inlineStr">
-        <is>
-          <t>Écart</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="29" t="inlineStr">
-        <is>
-          <t>Percolateurs 4 × 10 L (ABC LOCATION)</t>
-        </is>
-      </c>
-      <c r="C21" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D21" s="29" t="n">
-        <v>345</v>
-      </c>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="29">
-        <f>E21-D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="29" t="inlineStr">
-        <is>
-          <t>Friteuses × 2 (ABC LOCATION)</t>
-        </is>
-      </c>
-      <c r="C22" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D22" s="29" t="n">
-        <v>172</v>
-      </c>
-      <c r="E22" s="29" t="n"/>
-      <c r="F22" s="29">
-        <f>E22-D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="29" t="inlineStr">
-        <is>
-          <t>Machine pop-corn (location)</t>
-        </is>
-      </c>
-      <c r="C23" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D23" s="29" t="n">
-        <v>252</v>
-      </c>
-      <c r="E23" s="29" t="n"/>
-      <c r="F23" s="29">
-        <f>E23-D23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="29" t="inlineStr">
-        <is>
-          <t>Eau gratuite : fontaines + carafes (charge éthique)</t>
-        </is>
-      </c>
-      <c r="C24" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>400</v>
-      </c>
-      <c r="E24" s="29" t="n"/>
-      <c r="F24" s="29">
-        <f>E24-D24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>HACCP : tablier + charlotte + gants jetables + sonde T° + désinfectant</t>
-        </is>
-      </c>
-      <c r="C25" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>80</v>
-      </c>
-      <c r="E25" s="29" t="n"/>
-      <c r="F25" s="29">
-        <f>E25-D25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="n"/>
-      <c r="B26" s="29" t="inlineStr">
-        <is>
-          <t>Lavage écocups + sacs poubelles tri + récup huile usagée</t>
-        </is>
-      </c>
-      <c r="C26" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D26" s="29" t="n">
-        <v>120</v>
-      </c>
-      <c r="E26" s="29" t="n"/>
-      <c r="F26" s="29">
-        <f>E26-D26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="29" t="inlineStr">
-        <is>
-          <t>Trousse premiers secours buvette</t>
-        </is>
-      </c>
-      <c r="C27" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D27" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="29">
-        <f>E27-D27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="29" t="n"/>
-      <c r="B28" s="29" t="inlineStr">
-        <is>
-          <t>Affichage prix (ardoises + marqueurs) + caisse + ustensiles préparation</t>
-        </is>
-      </c>
-      <c r="C28" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D28" s="29" t="n">
-        <v>310</v>
-      </c>
-      <c r="E28" s="29" t="n"/>
-      <c r="F28" s="29">
-        <f>E28-D28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>TOTAL FIXES</t>
-        </is>
-      </c>
-      <c r="B29" s="30" t="n"/>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30">
-        <f>SUM(D21:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="30">
-        <f>SUM(E21:E28)</f>
-        <v/>
-      </c>
-      <c r="F29" s="30">
-        <f>E29-D29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>INVESTISSEMENT semi-fixe (amortissable sur éditions futures)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Prévu</t>
-        </is>
-      </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>Réel</t>
-        </is>
-      </c>
-      <c r="F33" s="28" t="inlineStr">
-        <is>
-          <t>Écart</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="29" t="n"/>
-      <c r="B34" s="29" t="inlineStr">
-        <is>
-          <t>Écocups réutilisables Atomic — 1 000 pièces 25 cL (réutilisables éditions futures)</t>
-        </is>
-      </c>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <t>Invest</t>
-        </is>
-      </c>
-      <c r="D34" s="29" t="n">
-        <v>600</v>
-      </c>
-      <c r="E34" s="29" t="n"/>
-      <c r="F34" s="29">
-        <f>E34-D34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>TOTAL INVEST</t>
-        </is>
-      </c>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="30">
-        <f>SUM(D34:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="30">
-        <f>SUM(E34:E34)</f>
-        <v/>
-      </c>
-      <c r="F35" s="30">
-        <f>E35-D35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="33" t="inlineStr">
-        <is>
-          <t>COÛTS VARIABLES (proportionnels à la fréquentation, ajustables)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="28" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B39" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C39" s="28" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D39" s="28" t="inlineStr">
-        <is>
-          <t>Prévu</t>
-        </is>
-      </c>
-      <c r="E39" s="28" t="inlineStr">
-        <is>
-          <t>Réel</t>
-        </is>
-      </c>
-      <c r="F39" s="28" t="inlineStr">
-        <is>
-          <t>Écart</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="29" t="n"/>
-      <c r="B40" s="29" t="inlineStr">
-        <is>
-          <t>Bière Le Pintadier — 10 fûts initial (commande ferme)</t>
-        </is>
-      </c>
-      <c r="C40" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D40" s="29" t="n">
-        <v>800</v>
-      </c>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="29">
-        <f>E40-D40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="29" t="n"/>
-      <c r="B41" s="29" t="inlineStr">
-        <is>
-          <t>Bière Le Pintadier — 5 fûts réassort éventuel (à activer vendredi soir si forte demande — +3200 € recettes)</t>
-        </is>
-      </c>
-      <c r="C41" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="29">
-        <f>E41-D41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="29" t="n"/>
-      <c r="B42" s="29" t="inlineStr">
-        <is>
-          <t>Vin Cubi Jura 5 L (Hyper Boisson, prix négocié 50 €/cubi) × 29 cubis</t>
-        </is>
-      </c>
-      <c r="C42" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D42" s="29" t="n">
-        <v>1450</v>
-      </c>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="29">
-        <f>E42-D42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="29" t="n"/>
-      <c r="B43" s="29" t="inlineStr">
-        <is>
-          <t>Soft : sirop 300 + jus 350 + Mortuacienne 58 + eau pét. 35 + eau plate 32</t>
-        </is>
-      </c>
-      <c r="C43" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D43" s="29" t="n">
-        <v>775</v>
-      </c>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="29">
-        <f>E43-D43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="29" t="n"/>
-      <c r="B44" s="29" t="inlineStr">
-        <is>
-          <t>Café : poudre BFC + sucre + lait + mélangeurs + gobelets bio</t>
-        </is>
-      </c>
-      <c r="C44" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D44" s="29" t="n">
-        <v>110</v>
-      </c>
-      <c r="E44" s="29" t="n"/>
-      <c r="F44" s="29">
-        <f>E44-D44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="29" t="n"/>
-      <c r="B45" s="29" t="inlineStr">
-        <is>
-          <t>Sucre bar additionnel + glace pilée bar</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D45" s="29" t="n">
-        <v>60</v>
-      </c>
-      <c r="E45" s="29" t="n"/>
-      <c r="F45" s="29">
-        <f>E45-D45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="29" t="n"/>
-      <c r="B46" s="29" t="inlineStr">
-        <is>
-          <t>Pop-corn (1 flousy=1,50€) : maïs 10kg (15) + huile/sel (8) + gobelets bio 72cL (40) — 405 portions</t>
-        </is>
-      </c>
-      <c r="C46" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D46" s="29" t="n">
-        <v>63</v>
-      </c>
-      <c r="E46" s="29" t="n"/>
-      <c r="F46" s="29">
-        <f>E46-D46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="29" t="n"/>
-      <c r="B47" s="29" t="inlineStr">
-        <is>
-          <t>Frites snack : pdt 50kg BFC (60) + huile (32) + sel (2) + barquettes (18) + sauces (36) — 360 portions</t>
-        </is>
-      </c>
-      <c r="C47" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D47" s="29" t="n">
-        <v>148</v>
-      </c>
-      <c r="E47" s="29" t="n"/>
-      <c r="F47" s="29">
-        <f>E47-D47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="29" t="n"/>
-      <c r="B48" s="29" t="inlineStr">
-        <is>
-          <t>Glaces ERHARD (1 boule=1,50€/2 boules=3€) : 39 bacs 2,5L (94) + cornets gaufrette 560 (67) + back-up (3) — 560 portions, mix 60/40</t>
-        </is>
-      </c>
-      <c r="C48" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D48" s="29" t="n">
-        <v>164</v>
-      </c>
-      <c r="E48" s="29" t="n"/>
-      <c r="F48" s="29">
-        <f>E48-D48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="29" t="n"/>
-      <c r="B49" s="29" t="inlineStr">
-        <is>
-          <t>Tomates cerise BRUNO (1 flousy=1,50€) : 75kg × 1,20€/kg (90) + gobelets bio 25cL (32) — 500 portions</t>
-        </is>
-      </c>
-      <c r="C49" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D49" s="29" t="n">
-        <v>122</v>
-      </c>
-      <c r="E49" s="29" t="n"/>
-      <c r="F49" s="29">
-        <f>E49-D49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="29" t="n"/>
-      <c r="B50" s="29" t="inlineStr">
-        <is>
-          <t>Assiettes : 770 grandes (3,07 €/u) + 330 petites (2,48 €/u) — mix 70% FC / 30% végé</t>
-        </is>
-      </c>
-      <c r="C50" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D50" s="29" t="n">
-        <v>3182</v>
-      </c>
-      <c r="E50" s="29" t="n"/>
-      <c r="F50" s="29">
-        <f>E50-D50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="29" t="n"/>
-      <c r="B51" s="29" t="inlineStr">
-        <is>
-          <t>Frites incluses dans grandes assiettes : 770 × 0,42 €</t>
-        </is>
-      </c>
-      <c r="C51" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D51" s="29" t="n">
-        <v>323</v>
-      </c>
-      <c r="E51" s="29" t="n"/>
-      <c r="F51" s="29">
-        <f>E51-D51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="29" t="n"/>
-      <c r="B52" s="29" t="inlineStr">
-        <is>
-          <t>Vaisselle bio jetable : gobelets soft+café+pop-corn + serviettes + back-up bière 300v</t>
-        </is>
-      </c>
-      <c r="C52" s="29" t="inlineStr">
-        <is>
-          <t>Dépense</t>
-        </is>
-      </c>
-      <c r="D52" s="29" t="n">
-        <v>319</v>
-      </c>
-      <c r="E52" s="29" t="n"/>
-      <c r="F52" s="29">
-        <f>E52-D52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="30" t="inlineStr">
-        <is>
-          <t>TOTAL VARIABLES</t>
-        </is>
-      </c>
-      <c r="B53" s="30" t="n"/>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="30">
-        <f>SUM(D40:D52)</f>
-        <v/>
-      </c>
-      <c r="E53" s="30">
-        <f>SUM(E40:E52)</f>
-        <v/>
-      </c>
-      <c r="F53" s="30">
-        <f>E53-D53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="34" t="inlineStr">
-        <is>
-          <t>SYNTHÈSE F&amp;B</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="30" t="n"/>
-      <c r="B57" s="30" t="inlineStr">
-        <is>
-          <t>TOTAL COÛTS F&amp;B (Fixes + Invest + Variables)</t>
-        </is>
-      </c>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="30">
-        <f>D29+D35+D53</f>
-        <v/>
-      </c>
-      <c r="E57" s="30">
-        <f>E29+E35+E53</f>
-        <v/>
-      </c>
-      <c r="F57" s="30">
-        <f>E57-D57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="30" t="n"/>
-      <c r="B58" s="30" t="inlineStr">
-        <is>
-          <t>TOTAL RECETTES F&amp;B</t>
-        </is>
-      </c>
-      <c r="C58" s="30" t="n"/>
-      <c r="D58" s="30">
-        <f>D16</f>
-        <v/>
-      </c>
-      <c r="E58" s="30">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="F58" s="30">
-        <f>E58-D58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="35" t="n"/>
-      <c r="B59" s="35" t="inlineStr">
-        <is>
-          <t>MARGE F&amp;B (sans réassort bière) — hors SACEM (Droits d'auteur) et hors repas artistes (Artistes)</t>
-        </is>
-      </c>
-      <c r="C59" s="35" t="n"/>
-      <c r="D59" s="35">
-        <f>D58-D57</f>
-        <v/>
-      </c>
-      <c r="E59" s="35">
-        <f>E58-E57</f>
-        <v/>
-      </c>
-      <c r="F59" s="35">
-        <f>E59-D59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="36" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1" s="18">
-      <c r="A62" s="37" t="inlineStr">
-        <is>
-          <t>• Réassort bière (5 fûts +400 € coûts ; +3 200 € recettes) : décision vendredi soir selon consommation observée</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1" s="18">
-      <c r="A63" s="37" t="inlineStr">
-        <is>
-          <t>• Marge avec réassort = ~24 882 € (vs 22 082 € sans). Activable à coût marginal nul.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1" s="18">
-      <c r="A64" s="37" t="inlineStr">
-        <is>
-          <t>• SACEM (4,4 % buvette) EXCLUE : à confirmer auprès de SACEM BFC qu'elle n'est pas due (déjà 8,8 % billetterie)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1" s="18">
-      <c r="A65" s="37" t="inlineStr">
-        <is>
-          <t>• Repas artistes (~555 €) EXCLUS : à imputer au budget Artistes (cohérence avec convention défraiement)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1" s="18">
-      <c r="A66" s="37" t="inlineStr">
-        <is>
-          <t>• Charges fixes 1 709 € + invest écocups 600 € = seuil de couverture ~127 fest cumulés (largement atteint)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1" s="18">
-      <c r="A67" s="37" t="inlineStr">
-        <is>
-          <t>• Marge variable par festivalier (sans réassort) = ~18,30 €/fest</t>
+      <c r="B119" s="30" t="n"/>
+      <c r="C119" s="30" t="n"/>
+      <c r="D119" s="30" t="n"/>
+      <c r="E119" s="30" t="n"/>
+      <c r="F119" s="30" t="n"/>
+      <c r="G119" s="30" t="n"/>
+      <c r="H119" s="30">
+        <f>H63</f>
+        <v/>
+      </c>
+      <c r="I119" s="30" t="n"/>
+      <c r="J119" s="30" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="30" t="inlineStr">
+        <is>
+          <t>TOTAL DÉPENSES F&amp;B</t>
+        </is>
+      </c>
+      <c r="B120" s="30" t="n"/>
+      <c r="C120" s="30" t="n"/>
+      <c r="D120" s="30" t="n"/>
+      <c r="E120" s="30" t="n"/>
+      <c r="F120" s="30" t="n"/>
+      <c r="G120" s="30" t="n"/>
+      <c r="H120" s="30">
+        <f>H115</f>
+        <v/>
+      </c>
+      <c r="I120" s="30" t="n"/>
+      <c r="J120" s="30" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="35" t="inlineStr">
+        <is>
+          <t>MARGE F&amp;B (sans réassort bière, hors SACEM, hors repas artistes)</t>
+        </is>
+      </c>
+      <c r="B121" s="35" t="n"/>
+      <c r="C121" s="35" t="n"/>
+      <c r="D121" s="35" t="n"/>
+      <c r="E121" s="35" t="n"/>
+      <c r="F121" s="35" t="n"/>
+      <c r="G121" s="35" t="n"/>
+      <c r="H121" s="35">
+        <f>H119-H120</f>
+        <v/>
+      </c>
+      <c r="I121" s="35" t="n"/>
+      <c r="J121" s="35" t="n"/>
+    </row>
+    <row r="123" ht="16" customHeight="1" s="18">
+      <c r="A123" s="37" t="inlineStr">
+        <is>
+          <t>NOTES IMPORTANTES :</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="16" customHeight="1" s="18">
+      <c r="A124" s="37" t="inlineStr">
+        <is>
+          <t>• SACEM Buvette 4,4 % (~1 427 €) : EXCLUE du F&amp;B - à confirmer non due (déjà 8,8 % billetterie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="16" customHeight="1" s="18">
+      <c r="A125" s="37" t="inlineStr">
+        <is>
+          <t>• SACEM Billetterie 8,8 % (~1 993 €) : payée septembre 2026 (post-festival, dans Frais divers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="16" customHeight="1" s="18">
+      <c r="A126" s="37" t="inlineStr">
+        <is>
+          <t>• Repas artistes (~555 €) : EXCLUS du F&amp;B - à imputer au budget Artistes</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1" s="18">
+      <c r="A127" s="37" t="inlineStr">
+        <is>
+          <t>• Coût gobelets bio (café, soft, pop-corn, tomates) inclus dans ligne globale "Vaisselle bio jetable" 319 € (Juillet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="16" customHeight="1" s="18">
+      <c r="A128" s="37" t="inlineStr">
+        <is>
+          <t>• Réassort bière 5 fûts : montant 0 € par défaut, à activer si forte demande (+400 € coût, +3 200 € recettes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1" s="18">
+      <c r="A129" s="37" t="inlineStr">
+        <is>
+          <t>• Volumes par jour estimés selon modulation Calibrage_buvette_2026.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A65:F65"/>
+  <mergeCells count="11">
+    <mergeCell ref="A117:J117"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A124:J124"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A128:J128"/>
+    <mergeCell ref="A129:J129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5208,7 +8417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="18" min="1" max="1"/>
@@ -5755,82 +8964,82 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="29" t="inlineStr">
-        <is>
-          <t>Artistes</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="inlineStr">
-        <is>
-          <t>Acompte 30% cachets artistes locaux/régionaux (signature contrats)</t>
-        </is>
-      </c>
-      <c r="D31" s="29" t="n">
-        <v>2100</v>
-      </c>
-      <c r="E31" s="29" t="inlineStr">
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="30" t="n"/>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total JUIN 2026</t>
+        </is>
+      </c>
+      <c r="D31" s="30">
+        <f>SUM(D23:D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="30" t="n"/>
+      <c r="F31" s="30" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>JUILLET 2026 — Dépenses prévues</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Échéance</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
+        <is>
+          <t>Pôle</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D35" s="28" t="inlineStr">
+        <is>
+          <t>Montant prévu</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="F35" s="28" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="n"/>
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>2ème vague communication + vidéo promo</t>
+        </is>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>500</v>
+      </c>
+      <c r="E36" s="29" t="inlineStr">
         <is>
           <t>Prévu</t>
         </is>
       </c>
-      <c r="F31" s="29" t="inlineStr">
-        <is>
-          <t>Sur ~7000 € locaux</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="30" t="n"/>
-      <c r="C32" s="30" t="inlineStr">
-        <is>
-          <t>Sous-total JUIN 2026</t>
-        </is>
-      </c>
-      <c r="D32" s="30">
-        <f>SUM(D23:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="30" t="n"/>
-      <c r="F32" s="30" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="33" t="inlineStr">
-        <is>
-          <t>JUILLET 2026 — Dépenses prévues</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>Échéance</t>
-        </is>
-      </c>
-      <c r="B36" s="28" t="inlineStr">
-        <is>
-          <t>Pôle</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D36" s="28" t="inlineStr">
-        <is>
-          <t>Montant prévu</t>
-        </is>
-      </c>
-      <c r="E36" s="28" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-      <c r="F36" s="28" t="inlineStr">
-        <is>
-          <t>Note</t>
+      <c r="F36" s="29" t="inlineStr">
+        <is>
+          <t>Final push avant festival</t>
         </is>
       </c>
     </row>
@@ -5838,16 +9047,16 @@
       <c r="A37" s="29" t="n"/>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Logistique</t>
         </is>
       </c>
       <c r="C37" s="29" t="inlineStr">
         <is>
-          <t>2ème vague communication + vidéo promo</t>
+          <t>Acompte 30% Toilettes / sanitaires</t>
         </is>
       </c>
       <c r="D37" s="29" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
@@ -5856,7 +9065,7 @@
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Final push avant festival</t>
+          <t>Sur 1500 €</t>
         </is>
       </c>
     </row>
@@ -5869,7 +9078,7 @@
       </c>
       <c r="C38" s="29" t="inlineStr">
         <is>
-          <t>Acompte 30% Toilettes / sanitaires</t>
+          <t>Acompte 30% Électricité / groupe électrogène</t>
         </is>
       </c>
       <c r="D38" s="29" t="n">
@@ -5895,11 +9104,11 @@
       </c>
       <c r="C39" s="29" t="inlineStr">
         <is>
-          <t>Acompte 30% Électricité / groupe électrogène</t>
+          <t>Acompte 30% Barrières / sécurité</t>
         </is>
       </c>
       <c r="D39" s="29" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
@@ -5908,7 +9117,7 @@
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Sur 1500 €</t>
+          <t>Sur 1000 €</t>
         </is>
       </c>
     </row>
@@ -5921,7 +9130,7 @@
       </c>
       <c r="C40" s="29" t="inlineStr">
         <is>
-          <t>Acompte 30% Barrières / sécurité</t>
+          <t>Acompte 30% Mobilier (tables, chaises, tentes)</t>
         </is>
       </c>
       <c r="D40" s="29" t="n">
@@ -5942,16 +9151,16 @@
       <c r="A41" s="29" t="n"/>
       <c r="B41" s="29" t="inlineStr">
         <is>
-          <t>Logistique</t>
+          <t>Artistes</t>
         </is>
       </c>
       <c r="C41" s="29" t="inlineStr">
         <is>
-          <t>Acompte 30% Mobilier (tables, chaises, tentes)</t>
+          <t>Répétitions Fabulo (4 art × 2 jours × 100 €)</t>
         </is>
       </c>
       <c r="D41" s="29" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
@@ -5960,7 +9169,7 @@
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>Sur 1000 €</t>
+          <t>Préparation collectif Fabulo</t>
         </is>
       </c>
     </row>
@@ -5973,22 +9182,18 @@
       </c>
       <c r="C42" s="29" t="inlineStr">
         <is>
-          <t>Répétitions Fabulo (4 art × 2 jours × 100 €)</t>
+          <t>Répétitions Atelier écriture — Sylvain (2j × 100 €)</t>
         </is>
       </c>
       <c r="D42" s="29" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
           <t>Prévu</t>
         </is>
       </c>
-      <c r="F42" s="29" t="inlineStr">
-        <is>
-          <t>Préparation collectif Fabulo</t>
-        </is>
-      </c>
+      <c r="F42" s="29" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="29" t="n"/>
@@ -5999,7 +9204,7 @@
       </c>
       <c r="C43" s="29" t="inlineStr">
         <is>
-          <t>Répétitions Atelier écriture — Sylvain (2j × 100 €)</t>
+          <t>Répétitions Atelier DJ — Jeff (2j × 100 €)</t>
         </is>
       </c>
       <c r="D43" s="29" t="n">
@@ -6021,33 +9226,37 @@
       </c>
       <c r="C44" s="29" t="inlineStr">
         <is>
-          <t>Répétitions Atelier DJ — Jeff (2j × 100 €)</t>
+          <t>Avance défraiement artistes étrangers (50% billets early)</t>
         </is>
       </c>
       <c r="D44" s="29" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E44" s="29" t="inlineStr">
         <is>
           <t>Prévu</t>
         </is>
       </c>
-      <c r="F44" s="29" t="inlineStr"/>
+      <c r="F44" s="29" t="inlineStr">
+        <is>
+          <t>Pour booking train/avion avant 15/06 deadline</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="29" t="n"/>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>Artistes</t>
+          <t>F&amp;B</t>
         </is>
       </c>
       <c r="C45" s="29" t="inlineStr">
         <is>
-          <t>Avance défraiement artistes étrangers (50% billets early)</t>
+          <t>Vaisselle bio jetable (gobelets, assiettes, serviettes)</t>
         </is>
       </c>
       <c r="D45" s="29" t="n">
-        <v>600</v>
+        <v>319</v>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
@@ -6056,7 +9265,7 @@
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>Pour booking train/avion avant 15/06 deadline</t>
+          <t>Stock pour J-2</t>
         </is>
       </c>
     </row>
@@ -6064,16 +9273,16 @@
       <c r="A46" s="29" t="n"/>
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>Artistes</t>
+          <t>F&amp;B</t>
         </is>
       </c>
       <c r="C46" s="29" t="inlineStr">
         <is>
-          <t>Acompte 20% supplémentaire cachets nationaux</t>
+          <t>HACCP (tablier, gants, sondes T°) + caisse + ustensiles préparation</t>
         </is>
       </c>
       <c r="D46" s="29" t="n">
-        <v>1400</v>
+        <v>540</v>
       </c>
       <c r="E46" s="29" t="inlineStr">
         <is>
@@ -6082,113 +9291,113 @@
       </c>
       <c r="F46" s="29" t="inlineStr">
         <is>
-          <t>Confirmation contrats</t>
+          <t>Préparation stand</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="n"/>
-      <c r="B47" s="29" t="inlineStr">
-        <is>
-          <t>F&amp;B</t>
-        </is>
-      </c>
-      <c r="C47" s="29" t="inlineStr">
-        <is>
-          <t>Vaisselle bio jetable (gobelets, assiettes, serviettes)</t>
-        </is>
-      </c>
-      <c r="D47" s="29" t="n">
-        <v>319</v>
-      </c>
-      <c r="E47" s="29" t="inlineStr">
+      <c r="A47" s="30" t="n"/>
+      <c r="B47" s="30" t="n"/>
+      <c r="C47" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total JUILLET 2026</t>
+        </is>
+      </c>
+      <c r="D47" s="30">
+        <f>SUM(D36:D46)</f>
+        <v/>
+      </c>
+      <c r="E47" s="30" t="n"/>
+      <c r="F47" s="30" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>AOÛT 2026 (avant festival 28/08) — Dépenses prévues</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
+          <t>Échéance</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="inlineStr">
+        <is>
+          <t>Pôle</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D51" s="28" t="inlineStr">
+        <is>
+          <t>Montant prévu</t>
+        </is>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="F51" s="28" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="n"/>
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Location salle La Grange Huguenet</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E52" s="29" t="inlineStr">
         <is>
           <t>Prévu</t>
         </is>
       </c>
-      <c r="F47" s="29" t="inlineStr">
-        <is>
-          <t>Stock pour J-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="29" t="n"/>
-      <c r="B48" s="29" t="inlineStr">
-        <is>
-          <t>F&amp;B</t>
-        </is>
-      </c>
-      <c r="C48" s="29" t="inlineStr">
-        <is>
-          <t>HACCP (tablier, gants, sondes T°) + caisse + ustensiles préparation</t>
-        </is>
-      </c>
-      <c r="D48" s="29" t="n">
-        <v>540</v>
-      </c>
-      <c r="E48" s="29" t="inlineStr">
+      <c r="F52" s="29" t="inlineStr">
+        <is>
+          <t>Au montage</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="n"/>
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>Logistique</t>
+        </is>
+      </c>
+      <c r="C53" s="29" t="inlineStr">
+        <is>
+          <t>Solde 70% Sonorisation</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E53" s="29" t="inlineStr">
         <is>
           <t>Prévu</t>
         </is>
       </c>
-      <c r="F48" s="29" t="inlineStr">
-        <is>
-          <t>Préparation stand</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="30" t="n"/>
-      <c r="B49" s="30" t="n"/>
-      <c r="C49" s="30" t="inlineStr">
-        <is>
-          <t>Sous-total JUILLET 2026</t>
-        </is>
-      </c>
-      <c r="D49" s="30">
-        <f>SUM(D37:D48)</f>
-        <v/>
-      </c>
-      <c r="E49" s="30" t="n"/>
-      <c r="F49" s="30" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="34" t="inlineStr">
-        <is>
-          <t>AOÛT 2026 (avant festival 28/08) — Dépenses prévues</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="28" t="inlineStr">
-        <is>
-          <t>Échéance</t>
-        </is>
-      </c>
-      <c r="B53" s="28" t="inlineStr">
-        <is>
-          <t>Pôle</t>
-        </is>
-      </c>
-      <c r="C53" s="28" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D53" s="28" t="inlineStr">
-        <is>
-          <t>Montant prévu</t>
-        </is>
-      </c>
-      <c r="E53" s="28" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-      <c r="F53" s="28" t="inlineStr">
-        <is>
-          <t>Note</t>
+      <c r="F53" s="29" t="inlineStr">
+        <is>
+          <t>Au montage J-2</t>
         </is>
       </c>
     </row>
@@ -6201,11 +9410,11 @@
       </c>
       <c r="C54" s="29" t="inlineStr">
         <is>
-          <t>Solde 70% Location salle La Grange Huguenet</t>
+          <t>Solde 70% Éclairage / lumière</t>
         </is>
       </c>
       <c r="D54" s="29" t="n">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
@@ -6214,7 +9423,7 @@
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>Au montage</t>
+          <t>Au montage J-2</t>
         </is>
       </c>
     </row>
@@ -6227,11 +9436,11 @@
       </c>
       <c r="C55" s="29" t="inlineStr">
         <is>
-          <t>Solde 70% Sonorisation</t>
+          <t>Solde 70% Scène / podium</t>
         </is>
       </c>
       <c r="D55" s="29" t="n">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
@@ -6253,11 +9462,11 @@
       </c>
       <c r="C56" s="29" t="inlineStr">
         <is>
-          <t>Solde 70% Éclairage / lumière</t>
+          <t>Solde 70% Toilettes / sanitaires</t>
         </is>
       </c>
       <c r="D56" s="29" t="n">
-        <v>1400</v>
+        <v>1050</v>
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
@@ -6266,7 +9475,7 @@
       </c>
       <c r="F56" s="29" t="inlineStr">
         <is>
-          <t>Au montage J-2</t>
+          <t>Au montage J-1</t>
         </is>
       </c>
     </row>
@@ -6279,11 +9488,11 @@
       </c>
       <c r="C57" s="29" t="inlineStr">
         <is>
-          <t>Solde 70% Scène / podium</t>
+          <t>Solde 70% Électricité / groupe électrogène</t>
         </is>
       </c>
       <c r="D57" s="29" t="n">
-        <v>1400</v>
+        <v>1050</v>
       </c>
       <c r="E57" s="29" t="inlineStr">
         <is>
@@ -6305,11 +9514,11 @@
       </c>
       <c r="C58" s="29" t="inlineStr">
         <is>
-          <t>Solde 70% Toilettes / sanitaires</t>
+          <t>Solde 70% Barrières / sécurité</t>
         </is>
       </c>
       <c r="D58" s="29" t="n">
-        <v>1050</v>
+        <v>700</v>
       </c>
       <c r="E58" s="29" t="inlineStr">
         <is>
@@ -6318,7 +9527,7 @@
       </c>
       <c r="F58" s="29" t="inlineStr">
         <is>
-          <t>Au montage J-1</t>
+          <t>Au montage J-2</t>
         </is>
       </c>
     </row>
@@ -6331,11 +9540,11 @@
       </c>
       <c r="C59" s="29" t="inlineStr">
         <is>
-          <t>Solde 70% Électricité / groupe électrogène</t>
+          <t>Solde 70% Mobilier (tables, chaises, tentes)</t>
         </is>
       </c>
       <c r="D59" s="29" t="n">
-        <v>1050</v>
+        <v>700</v>
       </c>
       <c r="E59" s="29" t="inlineStr">
         <is>
@@ -6344,7 +9553,7 @@
       </c>
       <c r="F59" s="29" t="inlineStr">
         <is>
-          <t>Au montage J-2</t>
+          <t>Au montage J-1</t>
         </is>
       </c>
     </row>
@@ -6352,16 +9561,16 @@
       <c r="A60" s="29" t="n"/>
       <c r="B60" s="29" t="inlineStr">
         <is>
-          <t>Logistique</t>
+          <t>F&amp;B</t>
         </is>
       </c>
       <c r="C60" s="29" t="inlineStr">
         <is>
-          <t>Solde 70% Barrières / sécurité</t>
+          <t>Solde Machine pop-corn (location)</t>
         </is>
       </c>
       <c r="D60" s="29" t="n">
-        <v>700</v>
+        <v>172</v>
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
@@ -6370,7 +9579,7 @@
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
-          <t>Au montage J-2</t>
+          <t>Au montage</t>
         </is>
       </c>
     </row>
@@ -6378,16 +9587,16 @@
       <c r="A61" s="29" t="n"/>
       <c r="B61" s="29" t="inlineStr">
         <is>
-          <t>Logistique</t>
+          <t>F&amp;B</t>
         </is>
       </c>
       <c r="C61" s="29" t="inlineStr">
         <is>
-          <t>Solde 70% Mobilier (tables, chaises, tentes)</t>
+          <t>Percolateurs 4×10L ABC LOCATION</t>
         </is>
       </c>
       <c r="D61" s="29" t="n">
-        <v>700</v>
+        <v>345</v>
       </c>
       <c r="E61" s="29" t="inlineStr">
         <is>
@@ -6396,7 +9605,7 @@
       </c>
       <c r="F61" s="29" t="inlineStr">
         <is>
-          <t>Au montage J-1</t>
+          <t>Réservation + livraison J-1</t>
         </is>
       </c>
     </row>
@@ -6409,7 +9618,7 @@
       </c>
       <c r="C62" s="29" t="inlineStr">
         <is>
-          <t>Solde Machine pop-corn (location)</t>
+          <t>Friteuses ×2 ABC LOCATION</t>
         </is>
       </c>
       <c r="D62" s="29" t="n">
@@ -6422,7 +9631,7 @@
       </c>
       <c r="F62" s="29" t="inlineStr">
         <is>
-          <t>Au montage</t>
+          <t>Réservation + livraison J-1</t>
         </is>
       </c>
     </row>
@@ -6435,11 +9644,11 @@
       </c>
       <c r="C63" s="29" t="inlineStr">
         <is>
-          <t>Percolateurs 4×10L ABC LOCATION</t>
+          <t>Eau gratuite — fontaines + carafes</t>
         </is>
       </c>
       <c r="D63" s="29" t="n">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="E63" s="29" t="inlineStr">
         <is>
@@ -6448,7 +9657,7 @@
       </c>
       <c r="F63" s="29" t="inlineStr">
         <is>
-          <t>Réservation + livraison J-1</t>
+          <t>Location J-1</t>
         </is>
       </c>
     </row>
@@ -6461,11 +9670,11 @@
       </c>
       <c r="C64" s="29" t="inlineStr">
         <is>
-          <t>Friteuses ×2 ABC LOCATION</t>
+          <t>Trousse premiers secours buvette + affichage</t>
         </is>
       </c>
       <c r="D64" s="29" t="n">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="E64" s="29" t="inlineStr">
         <is>
@@ -6474,7 +9683,7 @@
       </c>
       <c r="F64" s="29" t="inlineStr">
         <is>
-          <t>Réservation + livraison J-1</t>
+          <t>Préparation stand</t>
         </is>
       </c>
     </row>
@@ -6487,11 +9696,11 @@
       </c>
       <c r="C65" s="29" t="inlineStr">
         <is>
-          <t>Eau gratuite — fontaines + carafes</t>
+          <t>Sacs poubelles tri + lavage écocups + récup huile</t>
         </is>
       </c>
       <c r="D65" s="29" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="E65" s="29" t="inlineStr">
         <is>
@@ -6500,7 +9709,7 @@
       </c>
       <c r="F65" s="29" t="inlineStr">
         <is>
-          <t>Location J-1</t>
+          <t>Stand + préparation</t>
         </is>
       </c>
     </row>
@@ -6513,11 +9722,11 @@
       </c>
       <c r="C66" s="29" t="inlineStr">
         <is>
-          <t>Trousse premiers secours buvette + affichage</t>
+          <t>Bière Le Pintadier — 10 fûts initial</t>
         </is>
       </c>
       <c r="D66" s="29" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="E66" s="29" t="inlineStr">
         <is>
@@ -6526,7 +9735,7 @@
       </c>
       <c r="F66" s="29" t="inlineStr">
         <is>
-          <t>Préparation stand</t>
+          <t>Commande J-3, livraison J-1</t>
         </is>
       </c>
     </row>
@@ -6539,11 +9748,11 @@
       </c>
       <c r="C67" s="29" t="inlineStr">
         <is>
-          <t>Sacs poubelles tri + lavage écocups + récup huile</t>
+          <t>Vin Cubi Jura — 29 cubis (Hyper Boisson)</t>
         </is>
       </c>
       <c r="D67" s="29" t="n">
-        <v>120</v>
+        <v>1450</v>
       </c>
       <c r="E67" s="29" t="inlineStr">
         <is>
@@ -6552,7 +9761,7 @@
       </c>
       <c r="F67" s="29" t="inlineStr">
         <is>
-          <t>Stand + préparation</t>
+          <t>Commande J-7</t>
         </is>
       </c>
     </row>
@@ -6565,11 +9774,11 @@
       </c>
       <c r="C68" s="29" t="inlineStr">
         <is>
-          <t>Bière Le Pintadier — 10 fûts initial</t>
+          <t>Soft (sirop + jus + Mortuacienne + eaux 1L verre)</t>
         </is>
       </c>
       <c r="D68" s="29" t="n">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="E68" s="29" t="inlineStr">
         <is>
@@ -6578,7 +9787,7 @@
       </c>
       <c r="F68" s="29" t="inlineStr">
         <is>
-          <t>Commande J-3, livraison J-1</t>
+          <t>Commande J-7</t>
         </is>
       </c>
     </row>
@@ -6591,11 +9800,11 @@
       </c>
       <c r="C69" s="29" t="inlineStr">
         <is>
-          <t>Vin Cubi Jura — 29 cubis (Hyper Boisson)</t>
+          <t>Café moulu équitable BFC + sucre + lait + mélangeurs + gobelets</t>
         </is>
       </c>
       <c r="D69" s="29" t="n">
-        <v>1450</v>
+        <v>110</v>
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
@@ -6617,11 +9826,11 @@
       </c>
       <c r="C70" s="29" t="inlineStr">
         <is>
-          <t>Soft (sirop + jus + Mortuacienne + eaux 1L verre)</t>
+          <t>Sucre bar additionnel + glace pilée</t>
         </is>
       </c>
       <c r="D70" s="29" t="n">
-        <v>775</v>
+        <v>60</v>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
@@ -6630,7 +9839,7 @@
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Commande J-7</t>
+          <t>Achat J-1</t>
         </is>
       </c>
     </row>
@@ -6643,11 +9852,11 @@
       </c>
       <c r="C71" s="29" t="inlineStr">
         <is>
-          <t>Café moulu équitable BFC + sucre + lait + mélangeurs + gobelets</t>
+          <t>Assiettes : fromage Hôpitaux Vieux + Comté/Morbier (~70 kg)</t>
         </is>
       </c>
       <c r="D71" s="29" t="n">
-        <v>110</v>
+        <v>1100</v>
       </c>
       <c r="E71" s="29" t="inlineStr">
         <is>
@@ -6656,7 +9865,7 @@
       </c>
       <c r="F71" s="29" t="inlineStr">
         <is>
-          <t>Commande J-7</t>
+          <t>Commande J-3, livraison J-2</t>
         </is>
       </c>
     </row>
@@ -6669,11 +9878,11 @@
       </c>
       <c r="C72" s="29" t="inlineStr">
         <is>
-          <t>Sucre bar additionnel + glace pilée</t>
+          <t>Assiettes : charcuterie Ferme Ligny (~77 kg)</t>
         </is>
       </c>
       <c r="D72" s="29" t="n">
-        <v>60</v>
+        <v>1200</v>
       </c>
       <c r="E72" s="29" t="inlineStr">
         <is>
@@ -6682,7 +9891,7 @@
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
-          <t>Achat J-1</t>
+          <t>Commande J-3, livraison J-2</t>
         </is>
       </c>
     </row>
@@ -6695,11 +9904,11 @@
       </c>
       <c r="C73" s="29" t="inlineStr">
         <is>
-          <t>Assiettes : fromage Hôpitaux Vieux + Comté/Morbier (~70 kg)</t>
+          <t>Œufs Saveur de la Ferme (3 plateaux 360 + extras)</t>
         </is>
       </c>
       <c r="D73" s="29" t="n">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="E73" s="29" t="inlineStr">
         <is>
@@ -6721,11 +9930,11 @@
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>Assiettes : charcuterie Ferme Ligny (~77 kg)</t>
+          <t>Pain La Ronde des Pains (~110 pains 350g)</t>
         </is>
       </c>
       <c r="D74" s="29" t="n">
-        <v>1200</v>
+        <v>245</v>
       </c>
       <c r="E74" s="29" t="inlineStr">
         <is>
@@ -6734,7 +9943,7 @@
       </c>
       <c r="F74" s="29" t="inlineStr">
         <is>
-          <t>Commande J-3, livraison J-2</t>
+          <t>Commande J-3, livraison J-1</t>
         </is>
       </c>
     </row>
@@ -6747,11 +9956,11 @@
       </c>
       <c r="C75" s="29" t="inlineStr">
         <is>
-          <t>Œufs Saveur de la Ferme (3 plateaux 360 + extras)</t>
+          <t>Tomates cerise BRUNO BFC (~75 kg, restauration + snack)</t>
         </is>
       </c>
       <c r="D75" s="29" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="E75" s="29" t="inlineStr">
         <is>
@@ -6773,11 +9982,11 @@
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>Pain La Ronde des Pains (~110 pains 350g)</t>
+          <t>Pommes de terre BFC (~50 kg pour frites snack + grandes assiettes)</t>
         </is>
       </c>
       <c r="D76" s="29" t="n">
-        <v>245</v>
+        <v>60</v>
       </c>
       <c r="E76" s="29" t="inlineStr">
         <is>
@@ -6786,7 +9995,7 @@
       </c>
       <c r="F76" s="29" t="inlineStr">
         <is>
-          <t>Commande J-3, livraison J-1</t>
+          <t>Commande J-3, livraison J-2</t>
         </is>
       </c>
     </row>
@@ -6799,11 +10008,11 @@
       </c>
       <c r="C77" s="29" t="inlineStr">
         <is>
-          <t>Tomates cerise BRUNO BFC (~75 kg, restauration + snack)</t>
+          <t>Sachets sous vide Ferme Ligny + autres consommables resto</t>
         </is>
       </c>
       <c r="D77" s="29" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="E77" s="29" t="inlineStr">
         <is>
@@ -6812,7 +10021,7 @@
       </c>
       <c r="F77" s="29" t="inlineStr">
         <is>
-          <t>Commande J-3, livraison J-2</t>
+          <t>Avec commande charcuterie</t>
         </is>
       </c>
     </row>
@@ -6825,11 +10034,11 @@
       </c>
       <c r="C78" s="29" t="inlineStr">
         <is>
-          <t>Pommes de terre BFC (~50 kg pour frites snack + grandes assiettes)</t>
+          <t>Pop-corn (maïs 10kg + huile + sel + gobelets bio 72cL)</t>
         </is>
       </c>
       <c r="D78" s="29" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E78" s="29" t="inlineStr">
         <is>
@@ -6838,7 +10047,7 @@
       </c>
       <c r="F78" s="29" t="inlineStr">
         <is>
-          <t>Commande J-3, livraison J-2</t>
+          <t>Commande J-7</t>
         </is>
       </c>
     </row>
@@ -6851,11 +10060,11 @@
       </c>
       <c r="C79" s="29" t="inlineStr">
         <is>
-          <t>Sachets sous vide Ferme Ligny + autres consommables resto</t>
+          <t>Frites snack (huile friture + sel + barquettes kraft + sticks sauces)</t>
         </is>
       </c>
       <c r="D79" s="29" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="E79" s="29" t="inlineStr">
         <is>
@@ -6864,7 +10073,7 @@
       </c>
       <c r="F79" s="29" t="inlineStr">
         <is>
-          <t>Avec commande charcuterie</t>
+          <t>Commande J-7 (pdt comptées séparément)</t>
         </is>
       </c>
     </row>
@@ -6877,11 +10086,11 @@
       </c>
       <c r="C80" s="29" t="inlineStr">
         <is>
-          <t>Pop-corn (maïs 10kg + huile + sel + gobelets bio 72cL)</t>
+          <t>Glaces ERHARD (43 bacs 2,5L)</t>
         </is>
       </c>
       <c r="D80" s="29" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E80" s="29" t="inlineStr">
         <is>
@@ -6890,7 +10099,7 @@
       </c>
       <c r="F80" s="29" t="inlineStr">
         <is>
-          <t>Commande J-7</t>
+          <t>Commande J-3, livraison J-1</t>
         </is>
       </c>
     </row>
@@ -6903,11 +10112,11 @@
       </c>
       <c r="C81" s="29" t="inlineStr">
         <is>
-          <t>Frites snack (huile friture + sel + barquettes kraft + sticks sauces)</t>
+          <t>Cornets gaufrette comestibles (560 unités) + back-up</t>
         </is>
       </c>
       <c r="D81" s="29" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E81" s="29" t="inlineStr">
         <is>
@@ -6916,7 +10125,7 @@
       </c>
       <c r="F81" s="29" t="inlineStr">
         <is>
-          <t>Commande J-7 (pdt comptées séparément)</t>
+          <t>Commande J-7</t>
         </is>
       </c>
     </row>
@@ -6924,16 +10133,16 @@
       <c r="A82" s="29" t="n"/>
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>Artistes</t>
         </is>
       </c>
       <c r="C82" s="29" t="inlineStr">
         <is>
-          <t>Glaces ERHARD (43 bacs 2,5L)</t>
+          <t>Défraiement étrangers solde (sur réception justificatifs)</t>
         </is>
       </c>
       <c r="D82" s="29" t="n">
-        <v>101</v>
+        <v>1200</v>
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
@@ -6942,7 +10151,7 @@
       </c>
       <c r="F82" s="29" t="inlineStr">
         <is>
-          <t>Commande J-3, livraison J-1</t>
+          <t>Solde après réception tickets, payable J ou J+7</t>
         </is>
       </c>
     </row>
@@ -6950,16 +10159,16 @@
       <c r="A83" s="29" t="n"/>
       <c r="B83" s="29" t="inlineStr">
         <is>
-          <t>F&amp;B</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C83" s="29" t="inlineStr">
         <is>
-          <t>Cornets gaufrette comestibles (560 unités) + back-up</t>
+          <t>Frais administratifs divers (encres, fournitures bureau)</t>
         </is>
       </c>
       <c r="D83" s="29" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E83" s="29" t="inlineStr">
         <is>
@@ -6968,7 +10177,7 @@
       </c>
       <c r="F83" s="29" t="inlineStr">
         <is>
-          <t>Commande J-7</t>
+          <t>Préparation festival</t>
         </is>
       </c>
     </row>
@@ -6976,16 +10185,16 @@
       <c r="A84" s="29" t="n"/>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>Artistes</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C84" s="29" t="inlineStr">
         <is>
-          <t>Solde 50% cachets artistes (à régler post-prestation J+7)</t>
+          <t>Imprévus de dernière minute (provision)</t>
         </is>
       </c>
       <c r="D84" s="29" t="n">
-        <v>7000</v>
+        <v>500</v>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
@@ -6994,211 +10203,177 @@
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>Prévoir en trésorerie même si paiement J+7</t>
+          <t>Aléas</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29" t="n"/>
-      <c r="B85" s="29" t="inlineStr">
-        <is>
-          <t>Artistes</t>
-        </is>
-      </c>
-      <c r="C85" s="29" t="inlineStr">
-        <is>
-          <t>Défraiement étrangers solde (sur réception justificatifs)</t>
-        </is>
-      </c>
-      <c r="D85" s="29" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E85" s="29" t="inlineStr">
-        <is>
-          <t>Prévu</t>
-        </is>
-      </c>
-      <c r="F85" s="29" t="inlineStr">
-        <is>
-          <t>Solde après réception tickets, payable J ou J+7</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="29" t="n"/>
-      <c r="B86" s="29" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="C86" s="29" t="inlineStr">
-        <is>
-          <t>Frais administratifs divers (encres, fournitures bureau)</t>
-        </is>
-      </c>
-      <c r="D86" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="E86" s="29" t="inlineStr">
-        <is>
-          <t>Prévu</t>
-        </is>
-      </c>
-      <c r="F86" s="29" t="inlineStr">
-        <is>
-          <t>Préparation festival</t>
-        </is>
-      </c>
+      <c r="A85" s="30" t="n"/>
+      <c r="B85" s="30" t="n"/>
+      <c r="C85" s="30" t="inlineStr">
+        <is>
+          <t>Sous-total AOÛT 2026 (avant festival 28/08)</t>
+        </is>
+      </c>
+      <c r="D85" s="30">
+        <f>SUM(D52:D84)</f>
+        <v/>
+      </c>
+      <c r="E85" s="30" t="n"/>
+      <c r="F85" s="30" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="29" t="n"/>
-      <c r="B87" s="29" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="C87" s="29" t="inlineStr">
-        <is>
-          <t>Imprévus de dernière minute (provision)</t>
-        </is>
-      </c>
-      <c r="D87" s="29" t="n">
-        <v>500</v>
-      </c>
-      <c r="E87" s="29" t="inlineStr">
-        <is>
-          <t>Prévu</t>
-        </is>
-      </c>
-      <c r="F87" s="29" t="inlineStr">
-        <is>
-          <t>Aléas</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="30" t="n"/>
-      <c r="B88" s="30" t="n"/>
-      <c r="C88" s="30" t="inlineStr">
-        <is>
-          <t>Sous-total AOÛT 2026 (avant festival 28/08)</t>
-        </is>
-      </c>
-      <c r="D88" s="30">
-        <f>SUM(D54:D87)</f>
-        <v/>
-      </c>
-      <c r="E88" s="30" t="n"/>
-      <c r="F88" s="30" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="40" t="inlineStr">
+      <c r="A87" s="40" t="inlineStr">
         <is>
           <t>TOTAL DÉPENSES PRÉ-FESTIVAL (mai-août avant 28/08)</t>
         </is>
       </c>
-      <c r="B90" s="41" t="n"/>
-      <c r="C90" s="41" t="n"/>
-      <c r="D90" s="42" t="n">
-        <v>40650</v>
-      </c>
-      <c r="E90" s="41" t="n"/>
-      <c r="F90" s="41" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="36" t="inlineStr">
+      <c r="B87" s="41" t="n"/>
+      <c r="C87" s="41" t="n"/>
+      <c r="D87" s="42" t="n">
+        <v>30150</v>
+      </c>
+      <c r="E87" s="41" t="n"/>
+      <c r="F87" s="41" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="36" t="inlineStr">
         <is>
           <t>NOTES &amp; HYPOTHÈSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1" s="18">
+      <c r="A90" s="37" t="inlineStr">
+        <is>
+          <t>• Solde Qonto au 03/05/2026 : 1950 € — Besoin de trésorerie cumulé jusqu'au 27/08 : 30150 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1" s="18">
+      <c r="A91" s="37" t="inlineStr">
+        <is>
+          <t>• Gap à financer : 28200 € via crowdfunding + mécénat + subventions + early bird billetterie</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1" s="18">
+      <c r="A92" s="37" t="inlineStr">
+        <is>
+          <t>• Hypothèses fournisseurs : acompte 30% à la commande / solde 70% au montage (à confirmer avec chaque devis)</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="18">
       <c r="A93" s="37" t="inlineStr">
         <is>
-          <t>• Solde Qonto au 03/05/2026 : 1950 € — Besoin de trésorerie cumulé jusqu'au 27/08 : 40650 €</t>
+          <t>• Cachets artistes : 30% acompte signature contrat, 50% post-prestation J+7 (à confirmer convention)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1" s="18">
       <c r="A94" s="37" t="inlineStr">
         <is>
-          <t>• Gap à financer : 38700 € via crowdfunding + mécénat + subventions + early bird billetterie</t>
+          <t>• Défraiement étrangers : avance possible 50% pour booking précoce, solde sur justificatifs</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="18">
       <c r="A95" s="37" t="inlineStr">
         <is>
-          <t>• Hypothèses fournisseurs : acompte 30% à la commande / solde 70% au montage (à confirmer avec chaque devis)</t>
+          <t>• Matières fraîches F&amp;B : commandées J-3 (hors période 'pré-festival' stricte mais cash sortant avant recettes billetterie)</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1" s="18">
       <c r="A96" s="37" t="inlineStr">
         <is>
-          <t>• Cachets artistes : 30% acompte signature contrat, 50% post-prestation J+7 (à confirmer convention)</t>
+          <t>• SACEM Billetterie 1 993 € : payée septembre 2026 (post-festival, sur recettes réelles)</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1" s="18">
       <c r="A97" s="37" t="inlineStr">
         <is>
-          <t>• Défraiement étrangers : avance possible 50% pour booking précoce, solde sur justificatifs</t>
+          <t>• SACEM Buvette 1 427 € : exclue (à confirmer non due)</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1" s="18">
       <c r="A98" s="37" t="inlineStr">
         <is>
-          <t>• Matières fraîches F&amp;B : commandées J-3 (hors période 'pré-festival' stricte mais cash sortant avant recettes billetterie)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1" s="18">
-      <c r="A99" s="37" t="inlineStr">
-        <is>
-          <t>• SACEM Billetterie 1 993 € : payée septembre 2026 (post-festival, sur recettes réelles)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1" s="18">
-      <c r="A100" s="37" t="inlineStr">
-        <is>
-          <t>• SACEM Buvette 1 427 € : exclue (à confirmer non due)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1" s="18">
-      <c r="A101" s="37" t="inlineStr">
-        <is>
           <t>• Repas artistes 555 € : à imputer budget Artistes (non doublonné ici)</t>
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="43" t="inlineStr">
+        <is>
+          <t>POUR INFO — Dépenses POST-festival (non comptées ci-dessus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="44" t="n"/>
+      <c r="B101" s="44" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C101" s="44" t="inlineStr">
+        <is>
+          <t>Cachets artistes (TOUS payés post-festival, J+7)</t>
+        </is>
+      </c>
+      <c r="D101" s="44" t="n">
+        <v>15700</v>
+      </c>
+      <c r="E101" s="44" t="n"/>
+      <c r="F101" s="44" t="inlineStr">
+        <is>
+          <t>Septembre 2026 — décision Charles 03/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="44" t="n"/>
+      <c r="B102" s="44" t="inlineStr">
+        <is>
+          <t>Artistes</t>
+        </is>
+      </c>
+      <c r="C102" s="44" t="inlineStr">
+        <is>
+          <t>Défraiement artistes (étrangers - solde, locaux/régionaux)</t>
+        </is>
+      </c>
+      <c r="D102" s="44" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E102" s="44" t="n"/>
+      <c r="F102" s="44" t="inlineStr">
+        <is>
+          <t>Septembre 2026 — sur justificatifs</t>
+        </is>
+      </c>
+    </row>
     <row r="103">
-      <c r="A103" s="43" t="inlineStr">
-        <is>
-          <t>POUR INFO — Dépenses POST-festival (non comptées ci-dessus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="44" t="n"/>
-      <c r="B104" s="44" t="inlineStr">
+      <c r="A103" s="44" t="n"/>
+      <c r="B103" s="44" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="C104" s="44" t="inlineStr">
+      <c r="C103" s="44" t="inlineStr">
         <is>
           <t>SACEM Billetterie 8.8% (déclaration post-event)</t>
         </is>
       </c>
-      <c r="D104" s="44" t="n">
+      <c r="D103" s="44" t="n">
         <v>1993</v>
       </c>
-      <c r="E104" s="44" t="n"/>
-      <c r="F104" s="44" t="inlineStr">
+      <c r="E103" s="44" t="n"/>
+      <c r="F103" s="44" t="inlineStr">
         <is>
           <t>Septembre 2026 — sur recettes billetterie réelles</t>
         </is>
@@ -7206,17 +10381,17 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A92:F92"/>
     <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A87:C87"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A91:F91"/>
     <mergeCell ref="A97:F97"/>
-    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A100:F100"/>
     <mergeCell ref="A3:F3"/>
